--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -564,7 +564,7 @@
         <v>44350</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>44972</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44753</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44118</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44494</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>44412</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>44644</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>44838</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>44074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44350</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45125</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>44494</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>43741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45154</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44266</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>44645</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45119</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>43731</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>44263</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>44412</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45050</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>44964</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45181</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45201</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45030</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45030</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>44522</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>44972</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45205</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44838</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>45054</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45201</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>43805</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44095</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44474</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44838</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>44945</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45156</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45201</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44838</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>43336</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44095</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44266</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44838</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45119</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45201</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45201</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>43781</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44361</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45119</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45201</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45205</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>43731</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44678</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45201</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45205</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>43336</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43983</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44211</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45149</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>43381</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>43677</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44000</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44664</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45125</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>45132</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>44199</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>45205</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45208</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43608</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43726</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44609</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45050</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44000</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44206</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>43432</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>43987</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44039</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44382</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44420</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44732</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44972</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45113</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43523</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43658</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>43731</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>43923</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43924</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44235</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>44309</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>44401</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44518</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>44648</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44781</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45098</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>45112</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45125</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45233</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>43741</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>43775</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>43833</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>43837</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44141</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44195</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44476</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44494</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44531</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44532</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44560</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44638</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>44827</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>44852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44960</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44964</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44972</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44994</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45105</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>45166</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45240</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43332</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43332</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>43335</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>43340</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>43340</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>43347</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43350</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43360</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43370</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43370</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43370</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43375</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43375</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43377</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43377</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43377</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43377</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>43377</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43377</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43384</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43384</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43389</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>43389</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>43389</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>43395</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>43402</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>43409</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>43412</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>43412</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>43418</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43432</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>43432</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>43432</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>43432</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43440</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43444</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43448</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43451</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43467</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43472</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43472</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43475</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43476</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43476</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43479</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43480</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>43480</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>43480</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>43487</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>43496</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>43497</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>43500</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>43501</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>43503</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>43507</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>43509</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43509</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43509</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43509</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43523</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43523</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43523</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>43523</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>43542</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>43542</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>43542</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>43545</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>43545</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>43545</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>43558</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>43559</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>43559</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>43564</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>43592</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>43592</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>43594</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>43594</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>43608</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>43608</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>43612</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>43613</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>43614</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>43614</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>43640</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>43640</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>43640</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>43640</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>43640</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>43641</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>43648</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>43648</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>43656</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>43661</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43661</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>43664</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43664</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43664</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43665</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43682</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43690</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43699</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43700</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>43703</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>43705</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43712</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43714</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>43721</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>43726</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>43728</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>43731</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>43733</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>43733</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>43733</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>43739</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>43741</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>43746</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>43749</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>43749</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>43753</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>43755</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>43762</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>43762</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>43765</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>43774</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>43775</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>43791</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>43803</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>43805</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>43808</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>43810</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>43815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>43833</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>43833</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>43833</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>43837</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>43837</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>43838</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>43838</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>43854</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>43858</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>43858</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>43896</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>43896</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>43896</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>43896</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>43909</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>43910</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>43913</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>43913</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>43913</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>43913</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>43913</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>43913</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>43913</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>43913</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>43914</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>43915</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>43915</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>43915</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>43915</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>43923</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>43923</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>43923</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>43927</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>43935</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>43944</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>43945</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>43964</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>43964</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>43966</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>43966</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>43977</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>43983</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>43983</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>43986</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>43986</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44000</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>44000</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44007</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44007</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44022</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44032</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44036</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44039</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44060</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44064</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44064</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44069</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44071</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44075</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>44078</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44088</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44092</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44092</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44092</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>44092</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44092</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>44097</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>44105</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>44105</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44109</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44118</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>44129</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>44144</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44151</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44153</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44154</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44155</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44161</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44162</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44162</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>44165</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44169</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44172</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>44186</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>44186</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44193</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44195</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44208</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44211</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>44211</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44211</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>44216</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44216</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44235</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44235</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44235</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44235</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44235</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44235</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44235</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44237</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>44243</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>44246</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>44253</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>44253</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>44266</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44307</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44307</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44307</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44307</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44307</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44316</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44316</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44328</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44330</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44341</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44341</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44350</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44356</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44357</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44361</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44361</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44361</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44361</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44370</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44371</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44371</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44371</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44371</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44377</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44378</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>44382</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44386</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44389</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44389</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>44389</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44389</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44397</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44406</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44412</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44420</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>44420</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>44420</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44420</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>44420</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>44420</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44420</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>44419</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>44426</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>44433</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>44434</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44442</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44442</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44443</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44442</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>44452</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44452</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44452</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44452</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44452</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>44453</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44461</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44461</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>44462</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44469</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44470</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44473</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>44476</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>44476</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>44481</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>44482</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>44482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>44482</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44484</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44485</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44488</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44488</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44489</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44491</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44496</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44498</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44500</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>44502</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44503</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>44505</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>44511</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44515</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44515</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44515</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44522</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44522</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>44525</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44529</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>44531</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>44531</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44532</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44532</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44532</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44532</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>44533</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>44537</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44540</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44543</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44545</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44545</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44545</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44545</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>44545</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>44545</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44564</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>44567</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>44568</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>44578</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>44578</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>44594</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>44604</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>44609</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>44609</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>44615</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44615</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44617</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44617</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>44617</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>44617</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44617</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>44619</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44619</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44619</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44619</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44621</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44621</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44622</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44623</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44625</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44627</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44627</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44628</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44628</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44628</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44628</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44637</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44640</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         <v>44642</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>44657</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>44657</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>44658</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>44679</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44679</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44686</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44686</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44690</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44690</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>44692</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44693</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44693</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44698</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>44698</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>44700</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>44701</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>44708</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>44708</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44708</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44712</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>44713</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>44719</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>44726</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44725</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>44733</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38738,7 +38738,7 @@
         <v>44735</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>44735</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>44735</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44735</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>44741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44743</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44743</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>44743</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>44743</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44743</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>44743</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44743</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44743</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44743</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>44743</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44744</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>44744</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>44744</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44744</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>44744</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>44744</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44747</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>44747</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44748</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>44748</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>44754</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>44755</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>44756</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>44756</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>44757</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>44757</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>44757</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>44757</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>44773</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>44784</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>44784</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>44788</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44788</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>44788</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>44789</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44790</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>44797</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>44797</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41369,7 +41369,7 @@
         <v>44799</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>44798</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44799</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44799</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>44799</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44803</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>44802</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44802</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>44803</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44806</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>44805</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>44805</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44806</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>44810</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>44810</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>44813</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>44812</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44813</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44813</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44817</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44824</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>44824</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>44826</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>44827</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>44827</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>44826</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>44832</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>44831</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43204,7 +43204,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44834</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>44837</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>44837</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>44844</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>44847</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>44847</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>44847</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>44847</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>44847</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>44852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>44853</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>44852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>44853</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>44853</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>44852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>44853</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>44853</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>44855</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>44857</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>44859</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>44859</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>44858</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>44859</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44859</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>44858</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44859</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>44859</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>44859</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>44859</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>44862</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>44867</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44867</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45324,7 +45324,7 @@
         <v>44872</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>44874</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>44874</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>44875</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44879</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44879</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44881</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44881</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44888</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>44889</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>44889</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>44889</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44889</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44890</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44890</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>44890</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>44893</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>44896</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>44896</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>44901</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>44903</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>44903</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>44909</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>44909</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>44911</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>44911</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>44914</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>44917</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>44917</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>44917</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>44917</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>44920</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>44923</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44923</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>44923</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>44928</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>44930</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>44935</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>44936</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>44938</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>44938</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>44939</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>44939</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44939</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>44939</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>44939</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>44939</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>44939</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>44939</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44939</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>44939</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>44939</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>44939</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49127,7 +49127,7 @@
         <v>44942</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44943</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44944</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44944</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>44944</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>44945</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>44954</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>44955</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49878,7 +49878,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>44957</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>44960</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>44960</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>44960</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>44960</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>44960</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>44960</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>44963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>44971</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>44972</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>44972</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44972</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>44972</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>44972</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50959,7 +50959,7 @@
         <v>44972</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>44972</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>44972</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>44972</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>44972</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>44972</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>44972</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>44973</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>44978</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>44977</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>44977</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>44977</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>44978</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51755,7 +51755,7 @@
         <v>44981</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>44984</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>44985</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>44985</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>44985</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>44985</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>44985</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>44985</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>44987</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>44993</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>44993</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>44993</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>44994</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>44994</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>44995</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>45000</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52697,7 +52697,7 @@
         <v>45000</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>45000</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>45021</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52873,7 +52873,7 @@
         <v>45043</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45042</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>45043</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45048</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45048</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>45048</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53225,7 +53225,7 @@
         <v>45051</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45054</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>45056</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         <v>45056</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53463,7 +53463,7 @@
         <v>45057</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53525,7 +53525,7 @@
         <v>45062</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45076</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45084</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45084</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45084</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>45087</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53887,7 +53887,7 @@
         <v>45089</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>45089</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54001,7 +54001,7 @@
         <v>45089</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45090</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54120,7 +54120,7 @@
         <v>45090</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>45092</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>45093</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45092</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54363,7 +54363,7 @@
         <v>45092</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54420,7 +54420,7 @@
         <v>45093</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>45093</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
         <v>45096</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>45096</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45098</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>45098</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54777,7 +54777,7 @@
         <v>45099</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>45103</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54901,7 +54901,7 @@
         <v>45104</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54963,7 +54963,7 @@
         <v>45104</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>45104</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         <v>45104</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55149,7 +55149,7 @@
         <v>45105</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45106</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>45107</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45112</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45112</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45113</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45113</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45113</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45115</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45115</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45117</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>45117</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45119</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>45119</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45119</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>45125</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56126,7 +56126,7 @@
         <v>45125</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45140</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56411,7 +56411,7 @@
         <v>45143</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45142</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45148</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45148</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56721,7 +56721,7 @@
         <v>45147</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>45147</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>45148</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>45147</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45148</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57031,7 +57031,7 @@
         <v>45148</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>45149</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57150,7 +57150,7 @@
         <v>45149</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>45149</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57336,7 +57336,7 @@
         <v>45150</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57398,7 +57398,7 @@
         <v>45150</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57460,7 +57460,7 @@
         <v>45150</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45150</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45150</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45150</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>45152</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57765,7 +57765,7 @@
         <v>45152</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57822,7 +57822,7 @@
         <v>45155</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>45154</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>45155</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58003,7 +58003,7 @@
         <v>45154</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58065,7 +58065,7 @@
         <v>45155</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>45155</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58179,7 +58179,7 @@
         <v>45156</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58236,7 +58236,7 @@
         <v>45158</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58293,7 +58293,7 @@
         <v>45159</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58350,7 +58350,7 @@
         <v>45161</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>45161</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45162</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58536,7 +58536,7 @@
         <v>45161</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -58593,7 +58593,7 @@
         <v>45163</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45166</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45170</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58774,7 +58774,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>45170</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>45171</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58955,7 +58955,7 @@
         <v>45171</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59017,7 +59017,7 @@
         <v>45171</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59079,7 +59079,7 @@
         <v>45171</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45171</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45171</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59265,7 +59265,7 @@
         <v>45170</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45173</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45177</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59446,7 +59446,7 @@
         <v>45177</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>45177</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>45186</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>45187</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>45187</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59741,7 +59741,7 @@
         <v>45188</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59803,7 +59803,7 @@
         <v>45187</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59865,7 +59865,7 @@
         <v>45188</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59922,7 +59922,7 @@
         <v>45189</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59984,7 +59984,7 @@
         <v>45189</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60046,7 +60046,7 @@
         <v>45190</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45190</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45190</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45194</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60398,7 +60398,7 @@
         <v>45194</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         <v>45195</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60517,7 +60517,7 @@
         <v>45195</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45196</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>45196</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60698,7 +60698,7 @@
         <v>45196</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60817,7 +60817,7 @@
         <v>45195</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45198</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60941,7 +60941,7 @@
         <v>45199</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>45199</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>45203</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45203</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61189,7 +61189,7 @@
         <v>45203</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61313,7 +61313,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>45205</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45205</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>45205</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45205</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61685,7 +61685,7 @@
         <v>45205</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>45207</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61809,7 +61809,7 @@
         <v>45207</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61871,7 +61871,7 @@
         <v>45207</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>45207</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61995,7 +61995,7 @@
         <v>45208</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>45209</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62114,7 +62114,7 @@
         <v>45210</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62171,7 +62171,7 @@
         <v>45212</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62233,7 +62233,7 @@
         <v>45212</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>45212</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         <v>45217</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>45217</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62481,7 +62481,7 @@
         <v>45217</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45217</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45217</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>45217</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45217</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45216</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62848,7 +62848,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62910,7 +62910,7 @@
         <v>45217</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45217</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>45218</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63096,7 +63096,7 @@
         <v>45222</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63158,7 +63158,7 @@
         <v>45223</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63220,7 +63220,7 @@
         <v>45224</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63282,7 +63282,7 @@
         <v>45225</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>45226</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63406,7 +63406,7 @@
         <v>45225</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63468,7 +63468,7 @@
         <v>45226</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63530,7 +63530,7 @@
         <v>45226</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>45226</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63654,7 +63654,7 @@
         <v>45226</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>45227</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45229</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45229</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63892,7 +63892,7 @@
         <v>45230</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -63999,14 +63999,14 @@
     <row r="984" ht="15" customHeight="1">
       <c r="A984" t="inlineStr">
         <is>
-          <t>A 55706-2023</t>
+          <t>A 54316-2023</t>
         </is>
       </c>
       <c r="B984" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64019,7 +64019,7 @@
         </is>
       </c>
       <c r="G984" t="n">
-        <v>17.3</v>
+        <v>4.1</v>
       </c>
       <c r="H984" t="n">
         <v>0</v>
@@ -64056,14 +64056,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 54316-2023</t>
+          <t>A 55714-2023</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64076,7 +64076,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -64113,14 +64113,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 55714-2023</t>
+          <t>A 55688-2023</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64133,7 +64133,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -64177,7 +64177,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64227,14 +64227,14 @@
     <row r="988" ht="15" customHeight="1">
       <c r="A988" t="inlineStr">
         <is>
-          <t>A 55688-2023</t>
+          <t>A 55706-2023</t>
         </is>
       </c>
       <c r="B988" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64247,7 +64247,7 @@
         </is>
       </c>
       <c r="G988" t="n">
-        <v>6.4</v>
+        <v>17.3</v>
       </c>
       <c r="H988" t="n">
         <v>0</v>
@@ -64291,7 +64291,7 @@
         <v>45233</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64415,7 +64415,7 @@
         <v>45236</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64470,14 +64470,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 54983-2023</t>
+          <t>A 54981-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64495,7 +64495,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -64532,14 +64532,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 54981-2023</t>
+          <t>A 54985-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
-        <v>45237</v>
+        <v>45236</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64557,7 +64557,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -64594,14 +64594,14 @@
     <row r="994" ht="15" customHeight="1">
       <c r="A994" t="inlineStr">
         <is>
-          <t>A 54985-2023</t>
+          <t>A 54983-2023</t>
         </is>
       </c>
       <c r="B994" s="1" t="n">
-        <v>45236</v>
+        <v>45237</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64619,7 +64619,7 @@
         </is>
       </c>
       <c r="G994" t="n">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -64656,14 +64656,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 55326-2023</t>
+          <t>A 55327-2023</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64681,7 +64681,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -64718,14 +64718,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 55325-2023</t>
+          <t>A 55335-2023</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64743,7 +64743,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -64780,14 +64780,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 55327-2023</t>
+          <t>A 55325-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
-        <v>45238</v>
+        <v>45237</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64805,7 +64805,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -64842,14 +64842,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 55335-2023</t>
+          <t>A 55326-2023</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64867,7 +64867,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -64911,7 +64911,7 @@
         <v>45238</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64961,14 +64961,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 56747-2023</t>
+          <t>A 56754-2023</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -64986,7 +64986,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>16.2</v>
+        <v>17.7</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -65023,14 +65023,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 56847-2023</t>
+          <t>A 56763-2023</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65048,7 +65048,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -65085,14 +65085,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 56823-2023</t>
+          <t>A 56747-2023</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65110,7 +65110,7 @@
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>81.40000000000001</v>
+        <v>16.2</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -65147,14 +65147,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 56830-2023</t>
+          <t>A 56823-2023</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65172,7 +65172,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>66.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -65209,14 +65209,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 56758-2023</t>
+          <t>A 56847-2023</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65234,7 +65234,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>371.4</v>
+        <v>41</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -65271,14 +65271,14 @@
     <row r="1005" ht="15" customHeight="1">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>A 56754-2023</t>
+          <t>A 56758-2023</t>
         </is>
       </c>
       <c r="B1005" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65296,7 +65296,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>17.7</v>
+        <v>371.4</v>
       </c>
       <c r="H1005" t="n">
         <v>0</v>
@@ -65333,14 +65333,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 56763-2023</t>
+          <t>A 56830-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65358,7 +65358,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>78</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -65395,14 +65395,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 57246-2023</t>
+          <t>A 57108-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65415,7 +65415,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>15.3</v>
+        <v>0.6</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -65459,7 +65459,7 @@
         <v>45239</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65509,14 +65509,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 57108-2023</t>
+          <t>A 57137-2023</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65529,7 +65529,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>0.6</v>
+        <v>38.8</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -65566,14 +65566,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 57137-2023</t>
+          <t>A 57246-2023</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65586,7 +65586,7 @@
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>38.8</v>
+        <v>15.3</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -65630,7 +65630,7 @@
         <v>45240</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65680,14 +65680,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 56245-2023</t>
+          <t>A 56236-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65699,13 +65699,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1012" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1012" t="n">
-        <v>1.1</v>
+        <v>6.1</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -65742,14 +65737,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 56246-2023</t>
+          <t>A 56245-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65767,7 +65762,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -65804,14 +65799,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 56236-2023</t>
+          <t>A 56246-2023</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65823,8 +65818,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1014" t="n">
-        <v>6.1</v>
+        <v>3.9</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -65861,14 +65861,14 @@
     <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 57691-2023</t>
+          <t>A 56617-2023</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65881,7 +65881,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -65918,14 +65918,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 56617-2023</t>
+          <t>A 56622-2023</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65938,7 +65938,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -65975,14 +65975,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 56622-2023</t>
+          <t>A 57691-2023</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -65995,7 +65995,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -66039,7 +66039,7 @@
         <v>45244</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66096,7 +66096,7 @@
         <v>45244</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66153,7 +66153,7 @@
         <v>45245</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66210,7 +66210,7 @@
         <v>45247</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66272,7 +66272,7 @@
         <v>45248</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66329,7 +66329,7 @@
         <v>45251</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66391,7 +66391,7 @@
         <v>45251</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66448,7 +66448,7 @@
         <v>45251</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66505,7 +66505,7 @@
         <v>45251</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66562,7 +66562,7 @@
         <v>45251</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66619,7 +66619,7 @@
         <v>45252</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -66676,7 +66676,7 @@
         <v>45254</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66738,7 +66738,7 @@
         <v>45255</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66800,7 +66800,7 @@
         <v>45254</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66862,7 +66862,7 @@
         <v>45254</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>45259</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66976,7 +66976,7 @@
         <v>45260</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67033,7 +67033,7 @@
         <v>45260</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -564,7 +564,7 @@
         <v>44350</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>44972</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44753</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44118</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44494</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>44412</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>44644</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>44838</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>44074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44350</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45125</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>44494</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>43741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45154</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44266</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>44645</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45119</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>43731</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>44263</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>44412</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45050</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>44964</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45181</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45201</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45030</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45030</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>44522</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>44972</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45205</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44838</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>45054</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45201</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>43805</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44095</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44474</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44838</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>44945</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45156</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45201</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44838</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>43336</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44095</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44266</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44838</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45119</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45201</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45201</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>43781</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44361</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45119</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45201</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45205</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>43731</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44678</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45201</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45205</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>43336</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43983</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44211</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45149</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>43381</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>43677</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44000</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44664</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45125</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>45132</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>44199</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>45205</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45208</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43608</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43726</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44609</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45050</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44000</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44206</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>43432</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>43987</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44039</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44382</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44420</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44732</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44972</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45113</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43523</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43658</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>43731</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>43923</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43924</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44235</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>44309</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>44401</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44518</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>44648</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44781</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45098</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>45112</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45125</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45233</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>43741</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>43775</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>43833</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>43837</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44141</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44195</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44476</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44494</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44531</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44532</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44560</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44638</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>44827</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>44852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44960</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44964</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44972</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44994</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45105</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>45166</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45240</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43332</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43332</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>43335</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>43340</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>43340</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>43347</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43350</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43360</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43370</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43370</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43370</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43375</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43375</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43377</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43377</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43377</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43377</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>43377</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43377</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43384</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43384</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43389</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>43389</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>43389</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>43395</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>43402</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>43409</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>43412</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>43412</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>43418</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43432</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>43432</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>43432</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>43432</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43440</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43444</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43448</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43451</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43467</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43472</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43472</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43475</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43476</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43476</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43479</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43480</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>43480</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>43480</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>43487</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>43496</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>43497</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>43500</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>43501</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>43503</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>43507</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>43509</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43509</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43509</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43509</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43523</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43523</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43523</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>43523</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>43542</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>43542</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>43542</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>43545</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>43545</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>43545</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>43558</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>43559</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>43559</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>43564</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>43592</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>43592</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>43594</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>43594</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>43608</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>43608</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>43612</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>43613</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>43614</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>43614</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>43640</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>43640</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>43640</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>43640</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>43640</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>43641</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>43648</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>43648</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>43656</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>43661</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43661</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>43664</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43664</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43664</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43665</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43682</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43690</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43699</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43700</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>43703</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>43705</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43712</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43714</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>43721</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>43726</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>43728</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>43731</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>43733</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>43733</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>43733</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>43739</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>43741</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>43746</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>43749</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>43749</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>43753</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>43755</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>43762</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>43762</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>43765</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>43774</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>43775</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>43791</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>43803</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>43805</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>43808</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>43810</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>43815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>43833</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>43833</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>43833</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>43837</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>43837</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>43838</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>43838</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>43854</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>43858</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>43858</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>43896</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>43896</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>43896</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>43896</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>43909</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>43910</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>43913</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>43913</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>43913</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>43913</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>43913</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>43913</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>43913</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>43913</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>43914</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>43915</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>43915</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>43915</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>43915</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>43923</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>43923</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>43923</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>43927</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>43935</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>43944</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>43945</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>43964</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>43964</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>43966</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>43966</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>43977</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>43983</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>43983</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>43986</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>43986</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44000</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>44000</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44007</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44007</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44022</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44032</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44036</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44039</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44060</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44064</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44064</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44069</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44071</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44075</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>44078</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44088</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44092</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44092</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44092</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>44092</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44092</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>44097</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>44105</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>44105</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44109</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44118</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>44129</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>44144</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44151</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44153</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44154</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44155</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44161</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44162</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44162</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>44165</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44169</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44172</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>44186</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>44186</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44193</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44195</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44208</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44211</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>44211</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44211</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>44216</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44216</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44235</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44235</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44235</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44235</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44235</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44235</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44235</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44237</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>44243</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>44246</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>44253</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>44253</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>44266</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44307</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44307</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44307</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44307</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44307</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44316</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44316</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44328</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44330</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44341</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44341</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44350</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44356</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44357</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44361</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44361</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44361</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44361</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44370</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44371</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44371</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44371</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44371</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44377</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44378</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>44382</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44386</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44389</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44389</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>44389</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44389</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44397</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44406</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44412</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44420</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>44420</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>44420</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44420</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>44420</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>44420</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44420</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>44419</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>44426</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>44433</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>44434</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44442</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44442</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44443</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44442</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>44452</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44452</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44452</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44452</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44452</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>44453</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44461</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44461</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>44462</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44469</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44470</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44473</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>44476</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>44476</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>44481</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>44482</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>44482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>44482</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44484</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44485</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44488</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44488</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44489</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44491</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44496</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44498</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44500</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>44502</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44503</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>44505</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>44511</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44515</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44515</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44515</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44522</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44522</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>44525</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44529</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>44531</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>44531</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44532</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44532</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44532</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44532</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>44533</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>44537</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44540</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44543</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44545</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44545</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44545</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44545</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>44545</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>44545</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44564</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>44567</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>44568</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>44578</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>44578</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>44594</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>44604</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>44609</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>44609</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>44615</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44615</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44617</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44617</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>44617</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>44617</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44617</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>44619</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44619</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44619</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44619</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44621</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44621</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44622</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44623</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44625</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44627</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44627</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44628</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44628</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44628</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44628</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44637</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44640</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         <v>44642</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>44657</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>44657</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>44658</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>44679</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44679</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44686</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44686</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44690</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44690</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>44692</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44693</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44693</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44698</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>44698</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>44700</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>44701</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>44708</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>44708</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44708</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44712</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>44713</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>44719</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>44726</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44725</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>44733</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38738,7 +38738,7 @@
         <v>44735</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>44735</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>44735</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44735</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>44741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44743</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44743</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>44743</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>44743</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44743</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>44743</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44743</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44743</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44743</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>44743</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44744</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>44744</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>44744</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44744</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>44744</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>44744</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44747</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>44747</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44748</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>44748</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>44754</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>44755</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>44756</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>44756</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>44757</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>44757</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>44757</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>44757</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>44773</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>44784</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>44784</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>44788</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44788</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>44788</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>44789</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44790</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>44797</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>44797</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41369,7 +41369,7 @@
         <v>44799</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>44798</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44799</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44799</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>44799</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44803</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>44802</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44802</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>44803</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44806</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>44805</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>44805</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44806</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>44810</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>44810</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>44813</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>44812</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44813</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44813</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44817</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44824</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>44824</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>44826</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>44827</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>44827</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>44826</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>44832</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>44831</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43204,7 +43204,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44834</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>44837</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>44837</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>44844</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>44847</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>44847</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>44847</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>44847</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>44847</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>44852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>44853</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>44852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>44853</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>44853</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>44852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>44853</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>44853</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>44855</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>44857</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>44859</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>44859</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>44858</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>44859</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44859</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>44858</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44859</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>44859</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>44859</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>44859</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>44862</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>44867</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44867</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45324,7 +45324,7 @@
         <v>44872</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>44874</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>44874</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>44875</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44879</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44879</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44881</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44881</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44888</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>44889</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>44889</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>44889</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44889</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44890</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44890</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>44890</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>44893</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>44896</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>44896</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>44901</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>44903</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>44903</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>44909</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>44909</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>44911</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>44911</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>44914</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>44917</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>44917</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>44917</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>44917</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>44920</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>44923</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44923</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>44923</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>44928</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>44930</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>44935</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>44936</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>44938</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>44938</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>44939</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>44939</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44939</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>44939</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>44939</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>44939</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>44939</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>44939</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44939</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>44939</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>44939</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>44939</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49127,7 +49127,7 @@
         <v>44942</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44943</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44944</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44944</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>44944</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>44945</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>44954</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>44955</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49878,7 +49878,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>44957</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>44960</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>44960</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>44960</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>44960</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>44960</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>44960</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>44963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>44971</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>44972</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>44972</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44972</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>44972</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>44972</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50959,7 +50959,7 @@
         <v>44972</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>44972</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>44972</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>44972</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>44972</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>44972</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>44972</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>44973</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>44978</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>44977</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>44977</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>44977</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>44978</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51755,7 +51755,7 @@
         <v>44981</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>44984</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>44985</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>44985</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>44985</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>44985</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>44985</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>44985</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>44987</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>44993</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>44993</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>44993</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>44994</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>44994</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>44995</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>45000</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52697,7 +52697,7 @@
         <v>45000</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>45000</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>45021</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52873,7 +52873,7 @@
         <v>45043</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45042</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>45043</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45048</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45048</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>45048</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53225,7 +53225,7 @@
         <v>45051</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45054</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>45056</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         <v>45056</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53463,7 +53463,7 @@
         <v>45057</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53525,7 +53525,7 @@
         <v>45062</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45076</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45084</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45084</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45084</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>45087</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53887,7 +53887,7 @@
         <v>45089</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>45089</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54001,7 +54001,7 @@
         <v>45089</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45090</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54120,7 +54120,7 @@
         <v>45090</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>45092</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>45093</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45092</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54363,7 +54363,7 @@
         <v>45092</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54420,7 +54420,7 @@
         <v>45093</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>45093</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
         <v>45096</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>45096</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45098</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>45098</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54777,7 +54777,7 @@
         <v>45099</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>45103</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54901,7 +54901,7 @@
         <v>45104</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54963,7 +54963,7 @@
         <v>45104</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>45104</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         <v>45104</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55149,7 +55149,7 @@
         <v>45105</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45106</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>45107</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45112</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45112</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45113</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45113</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45113</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45115</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45115</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45117</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>45117</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45119</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>45119</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45119</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>45125</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56126,7 +56126,7 @@
         <v>45125</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45140</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56411,7 +56411,7 @@
         <v>45143</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45142</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45148</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45148</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56721,7 +56721,7 @@
         <v>45147</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>45147</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>45148</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>45147</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45148</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57031,7 +57031,7 @@
         <v>45148</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>45149</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57150,7 +57150,7 @@
         <v>45149</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>45149</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57336,7 +57336,7 @@
         <v>45150</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57398,7 +57398,7 @@
         <v>45150</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57460,7 +57460,7 @@
         <v>45150</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45150</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45150</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45150</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>45152</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57765,7 +57765,7 @@
         <v>45152</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57822,7 +57822,7 @@
         <v>45155</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>45154</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>45155</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58003,7 +58003,7 @@
         <v>45154</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58065,7 +58065,7 @@
         <v>45155</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>45155</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58179,7 +58179,7 @@
         <v>45156</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58236,7 +58236,7 @@
         <v>45158</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58293,7 +58293,7 @@
         <v>45159</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58350,7 +58350,7 @@
         <v>45161</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>45161</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45162</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58536,7 +58536,7 @@
         <v>45161</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -58593,7 +58593,7 @@
         <v>45163</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45166</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45170</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58774,7 +58774,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>45170</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>45171</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58955,7 +58955,7 @@
         <v>45171</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59017,7 +59017,7 @@
         <v>45171</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59079,7 +59079,7 @@
         <v>45171</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45171</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45171</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59265,7 +59265,7 @@
         <v>45170</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45173</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45177</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59446,7 +59446,7 @@
         <v>45177</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>45177</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>45186</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>45187</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>45187</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59741,7 +59741,7 @@
         <v>45188</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59803,7 +59803,7 @@
         <v>45187</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59865,7 +59865,7 @@
         <v>45188</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59922,7 +59922,7 @@
         <v>45189</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59984,7 +59984,7 @@
         <v>45189</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60046,7 +60046,7 @@
         <v>45190</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45190</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45190</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45194</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60398,7 +60398,7 @@
         <v>45194</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         <v>45195</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60517,7 +60517,7 @@
         <v>45195</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45196</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>45196</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60698,7 +60698,7 @@
         <v>45196</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60817,7 +60817,7 @@
         <v>45195</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45198</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60941,7 +60941,7 @@
         <v>45199</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>45199</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>45203</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45203</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61189,7 +61189,7 @@
         <v>45203</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61313,7 +61313,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>45205</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45205</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>45205</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45205</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61685,7 +61685,7 @@
         <v>45205</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>45207</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61809,7 +61809,7 @@
         <v>45207</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61871,7 +61871,7 @@
         <v>45207</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>45207</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61995,7 +61995,7 @@
         <v>45208</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>45209</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62114,7 +62114,7 @@
         <v>45210</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62171,7 +62171,7 @@
         <v>45212</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62233,7 +62233,7 @@
         <v>45212</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>45212</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         <v>45217</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>45217</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62481,7 +62481,7 @@
         <v>45217</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45217</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45217</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>45217</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45217</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45216</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62848,7 +62848,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62910,7 +62910,7 @@
         <v>45217</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45217</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>45218</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63096,7 +63096,7 @@
         <v>45222</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63158,7 +63158,7 @@
         <v>45223</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63220,7 +63220,7 @@
         <v>45224</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63282,7 +63282,7 @@
         <v>45225</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>45226</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63406,7 +63406,7 @@
         <v>45225</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63468,7 +63468,7 @@
         <v>45226</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63530,7 +63530,7 @@
         <v>45226</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>45226</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63654,7 +63654,7 @@
         <v>45226</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>45227</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45229</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45229</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63892,7 +63892,7 @@
         <v>45230</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -64006,7 +64006,7 @@
         <v>45232</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64063,7 +64063,7 @@
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64120,7 +64120,7 @@
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64234,7 +64234,7 @@
         <v>45232</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>45233</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64408,14 +64408,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 54984-2023</t>
+          <t>A 54983-2023</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
-        <v>45236</v>
+        <v>45237</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64433,7 +64433,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -64470,14 +64470,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 54981-2023</t>
+          <t>A 54984-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
-        <v>45237</v>
+        <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64495,7 +64495,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -64532,14 +64532,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 54985-2023</t>
+          <t>A 54981-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
-        <v>45236</v>
+        <v>45237</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64557,7 +64557,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>7.5</v>
+        <v>3.3</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -64594,14 +64594,14 @@
     <row r="994" ht="15" customHeight="1">
       <c r="A994" t="inlineStr">
         <is>
-          <t>A 54983-2023</t>
+          <t>A 54985-2023</t>
         </is>
       </c>
       <c r="B994" s="1" t="n">
-        <v>45237</v>
+        <v>45236</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64619,7 +64619,7 @@
         </is>
       </c>
       <c r="G994" t="n">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -64656,14 +64656,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 55327-2023</t>
+          <t>A 55326-2023</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64681,7 +64681,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -64718,14 +64718,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 55335-2023</t>
+          <t>A 55327-2023</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64743,7 +64743,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -64780,14 +64780,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 55325-2023</t>
+          <t>A 55335-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64805,7 +64805,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -64842,14 +64842,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 55326-2023</t>
+          <t>A 55325-2023</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
-        <v>45238</v>
+        <v>45237</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64867,7 +64867,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -64911,7 +64911,7 @@
         <v>45238</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64961,14 +64961,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 56754-2023</t>
+          <t>A 56758-2023</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -64986,7 +64986,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>17.7</v>
+        <v>371.4</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -65023,14 +65023,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 56763-2023</t>
+          <t>A 56830-2023</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65048,7 +65048,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>78</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -65092,7 +65092,7 @@
         <v>45238</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65147,14 +65147,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 56823-2023</t>
+          <t>A 56754-2023</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65172,7 +65172,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>81.40000000000001</v>
+        <v>17.7</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -65209,14 +65209,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 56847-2023</t>
+          <t>A 56763-2023</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65234,7 +65234,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -65271,14 +65271,14 @@
     <row r="1005" ht="15" customHeight="1">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>A 56758-2023</t>
+          <t>A 56823-2023</t>
         </is>
       </c>
       <c r="B1005" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65296,7 +65296,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>371.4</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H1005" t="n">
         <v>0</v>
@@ -65333,14 +65333,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 56830-2023</t>
+          <t>A 56847-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65358,7 +65358,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>66.90000000000001</v>
+        <v>41</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -65402,7 +65402,7 @@
         <v>45239</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65452,14 +65452,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 57123-2023</t>
+          <t>A 57246-2023</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65472,7 +65472,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>16.1</v>
+        <v>15.3</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -65509,14 +65509,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 57137-2023</t>
+          <t>A 57123-2023</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65529,7 +65529,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>38.8</v>
+        <v>16.1</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -65566,14 +65566,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 57246-2023</t>
+          <t>A 57137-2023</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65586,7 +65586,7 @@
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>15.3</v>
+        <v>38.8</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -65630,7 +65630,7 @@
         <v>45240</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65680,14 +65680,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 56236-2023</t>
+          <t>A 56246-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65699,8 +65699,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1012" t="n">
-        <v>6.1</v>
+        <v>3.9</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -65737,14 +65742,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 56245-2023</t>
+          <t>A 56236-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65756,13 +65761,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1013" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1013" t="n">
-        <v>1.1</v>
+        <v>6.1</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -65799,14 +65799,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 56246-2023</t>
+          <t>A 56245-2023</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65824,7 +65824,7 @@
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -65868,7 +65868,7 @@
         <v>45243</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>45243</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65982,7 +65982,7 @@
         <v>45243</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -66032,14 +66032,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 57058-2023</t>
+          <t>A 57057-2023</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66052,7 +66052,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -66089,14 +66089,14 @@
     <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>A 57057-2023</t>
+          <t>A 57058-2023</t>
         </is>
       </c>
       <c r="B1019" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66109,7 +66109,7 @@
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -66153,7 +66153,7 @@
         <v>45245</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66210,7 +66210,7 @@
         <v>45247</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66272,7 +66272,7 @@
         <v>45248</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66329,7 +66329,7 @@
         <v>45251</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66384,14 +66384,14 @@
     <row r="1024" ht="15" customHeight="1">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>A 58749-2023</t>
+          <t>A 59110-2023</t>
         </is>
       </c>
       <c r="B1024" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66404,7 +66404,7 @@
         </is>
       </c>
       <c r="G1024" t="n">
-        <v>2.8</v>
+        <v>10.1</v>
       </c>
       <c r="H1024" t="n">
         <v>0</v>
@@ -66441,14 +66441,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 58756-2023</t>
+          <t>A 58749-2023</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66461,7 +66461,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -66498,14 +66498,14 @@
     <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>A 59117-2023</t>
+          <t>A 58756-2023</t>
         </is>
       </c>
       <c r="B1026" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66518,7 +66518,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -66555,14 +66555,14 @@
     <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 59110-2023</t>
+          <t>A 59117-2023</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66575,7 +66575,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -66619,7 +66619,7 @@
         <v>45252</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -66669,14 +66669,14 @@
     <row r="1029" ht="15" customHeight="1">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>A 59663-2023</t>
+          <t>A 59664-2023</t>
         </is>
       </c>
       <c r="B1029" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66694,7 +66694,7 @@
         </is>
       </c>
       <c r="G1029" t="n">
-        <v>12.8</v>
+        <v>3.3</v>
       </c>
       <c r="H1029" t="n">
         <v>0</v>
@@ -66731,14 +66731,14 @@
     <row r="1030" ht="15" customHeight="1">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>A 59671-2023</t>
+          <t>A 59663-2023</t>
         </is>
       </c>
       <c r="B1030" s="1" t="n">
-        <v>45255</v>
+        <v>45254</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66756,7 +66756,7 @@
         </is>
       </c>
       <c r="G1030" t="n">
-        <v>1.3</v>
+        <v>12.8</v>
       </c>
       <c r="H1030" t="n">
         <v>0</v>
@@ -66793,14 +66793,14 @@
     <row r="1031" ht="15" customHeight="1">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>A 59664-2023</t>
+          <t>A 60035-2023</t>
         </is>
       </c>
       <c r="B1031" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66812,13 +66812,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1031" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1031" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="H1031" t="n">
         <v>0</v>
@@ -66855,14 +66850,14 @@
     <row r="1032" ht="15" customHeight="1">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>A 60035-2023</t>
+          <t>A 59671-2023</t>
         </is>
       </c>
       <c r="B1032" s="1" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66874,8 +66869,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1032" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="H1032" t="n">
         <v>0</v>
@@ -66919,7 +66919,7 @@
         <v>45259</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66969,14 +66969,14 @@
     <row r="1034" ht="15" customHeight="1">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>A 60842-2023</t>
+          <t>A 60841-2023</t>
         </is>
       </c>
       <c r="B1034" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -66989,7 +66989,7 @@
         </is>
       </c>
       <c r="G1034" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="H1034" t="n">
         <v>0</v>
@@ -67026,14 +67026,14 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>A 60841-2023</t>
+          <t>A 60842-2023</t>
         </is>
       </c>
       <c r="B1035" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -67046,7 +67046,7 @@
         </is>
       </c>
       <c r="G1035" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="H1035" t="n">
         <v>0</v>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -564,7 +564,7 @@
         <v>44350</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>44972</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44753</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44118</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44494</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>44412</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>44644</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>44838</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>44074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44350</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45125</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>44494</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>43741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45154</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44266</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>44645</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45119</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>43731</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>44263</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>44412</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45050</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>44964</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45181</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45201</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45030</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45030</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>44522</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>44972</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45205</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44838</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>45054</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45201</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>43805</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44095</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44474</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44838</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>44945</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45156</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45201</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44838</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>43336</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44095</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44266</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44838</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45119</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45201</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45201</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>43781</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44361</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45119</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45201</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45205</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>43731</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44678</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45201</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45205</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>43336</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43983</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44211</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45149</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>43381</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>43677</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44000</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44664</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45125</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>45132</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>44199</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>45205</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45208</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43608</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43726</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44609</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45050</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44000</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44206</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>43432</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>43987</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44039</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44382</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44420</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44732</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44972</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45113</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43523</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43658</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>43731</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>43923</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43924</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44235</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>44309</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>44401</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44518</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>44648</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44781</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45098</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>45112</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45125</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45233</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>43741</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>43775</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>43833</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>43837</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44141</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44195</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44476</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44494</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44531</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44532</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44560</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44638</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>44827</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>44852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44960</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44964</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44972</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44994</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45105</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>45166</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45240</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43332</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43332</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>43335</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>43340</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>43340</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>43347</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43350</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43360</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43370</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43370</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43370</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43375</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43375</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43377</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43377</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43377</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43377</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>43377</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43377</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43384</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43384</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43389</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>43389</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>43389</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>43395</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>43402</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>43409</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>43412</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>43412</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>43418</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43432</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>43432</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>43432</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>43432</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43440</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43444</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43448</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43451</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43467</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43472</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43472</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43475</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43476</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43476</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43479</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43480</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>43480</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>43480</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>43487</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>43496</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>43497</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>43500</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>43501</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>43503</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>43507</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>43509</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43509</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43509</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43509</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43523</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43523</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43523</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>43523</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>43542</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>43542</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>43542</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>43545</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>43545</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>43545</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>43558</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>43559</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>43559</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>43564</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>43592</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>43592</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>43594</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>43594</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>43608</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>43608</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>43612</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>43613</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>43614</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>43614</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>43640</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>43640</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>43640</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>43640</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>43640</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>43641</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>43648</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>43648</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>43656</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>43661</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43661</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>43664</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43664</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43664</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43665</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43682</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43690</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43699</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43700</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>43703</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>43705</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43712</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43714</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>43721</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>43726</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>43728</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>43731</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>43733</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>43733</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>43733</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>43739</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>43741</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>43746</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>43749</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>43749</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>43753</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>43755</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>43762</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>43762</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>43765</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>43774</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>43775</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>43791</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>43803</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>43805</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>43808</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>43810</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>43815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>43833</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>43833</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>43833</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>43837</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>43837</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>43838</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>43838</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>43854</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>43858</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>43858</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>43896</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>43896</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>43896</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>43896</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>43909</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>43910</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>43913</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>43913</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>43913</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>43913</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>43913</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>43913</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>43913</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>43913</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>43914</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>43915</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>43915</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>43915</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>43915</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>43923</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>43923</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>43923</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>43927</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>43935</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>43944</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>43945</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>43964</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>43964</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>43966</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>43966</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>43977</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>43983</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>43983</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>43986</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>43986</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44000</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>44000</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44007</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44007</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44022</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44032</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44036</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44039</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44060</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44064</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44064</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44069</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44071</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44075</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>44078</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44088</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44092</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44092</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44092</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>44092</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44092</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>44097</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>44105</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>44105</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44109</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44118</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>44129</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>44144</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44151</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44153</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44154</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44155</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44161</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44162</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44162</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>44165</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44169</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44172</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>44186</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>44186</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44193</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44195</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44208</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44211</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>44211</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44211</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>44216</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44216</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44235</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44235</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44235</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44235</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44235</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44235</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44235</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44237</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>44243</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>44246</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>44253</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>44253</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>44266</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44307</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44307</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44307</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44307</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44307</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44316</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44316</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44328</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44330</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44341</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44341</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44350</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44356</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44357</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44361</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44361</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44361</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44361</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44370</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44371</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44371</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44371</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44371</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44377</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44378</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>44382</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44386</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44389</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44389</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>44389</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44389</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44397</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44406</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44412</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44420</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>44420</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>44420</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44420</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>44420</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>44420</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44420</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>44419</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>44426</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>44433</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>44434</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44442</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44442</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44443</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44442</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>44452</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44452</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44452</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44452</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44452</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>44453</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44461</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44461</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>44462</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44469</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44470</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44473</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>44476</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>44476</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>44481</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>44482</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>44482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>44482</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44484</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44485</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44488</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44488</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44489</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44491</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44496</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44498</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44500</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>44502</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44503</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>44505</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>44511</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44515</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44515</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44515</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44522</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44522</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>44525</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44529</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>44531</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>44531</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44532</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44532</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44532</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44532</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>44533</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>44537</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44540</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44543</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44545</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44545</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44545</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44545</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>44545</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>44545</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44564</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>44567</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>44568</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>44578</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>44578</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>44594</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>44604</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>44609</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>44609</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>44615</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44615</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44617</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44617</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>44617</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>44617</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44617</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>44619</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44619</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44619</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44619</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44621</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44621</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44622</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44623</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44625</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44627</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44627</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44628</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44628</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44628</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44628</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44637</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44640</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         <v>44642</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>44657</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>44657</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>44658</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>44679</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44679</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44686</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44686</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44690</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44690</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>44692</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44693</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44693</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44698</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>44698</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>44700</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>44701</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>44708</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>44708</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44708</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44712</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>44713</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>44719</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>44726</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44725</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>44733</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38738,7 +38738,7 @@
         <v>44735</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>44735</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>44735</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44735</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>44741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44743</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44743</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>44743</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>44743</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44743</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>44743</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44743</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44743</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44743</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>44743</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44744</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>44744</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>44744</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44744</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>44744</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>44744</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44747</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>44747</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44748</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>44748</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>44754</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>44755</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>44756</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>44756</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>44757</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>44757</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>44757</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>44757</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>44773</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>44784</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>44784</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>44788</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44788</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>44788</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>44789</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44790</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>44797</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>44797</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41369,7 +41369,7 @@
         <v>44799</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>44798</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44799</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44799</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>44799</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44803</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>44802</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44802</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>44803</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44806</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>44805</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>44805</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44806</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>44810</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>44810</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>44813</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>44812</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44813</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44813</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44817</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44824</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>44824</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>44826</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>44827</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>44827</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>44826</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>44832</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>44831</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43204,7 +43204,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44834</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>44837</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>44837</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>44844</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>44847</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>44847</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>44847</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>44847</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>44847</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>44852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>44853</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>44852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>44853</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>44853</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>44852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>44853</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>44853</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>44855</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>44857</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>44859</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>44859</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>44858</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>44859</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44859</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>44858</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44859</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>44859</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>44859</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>44859</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>44862</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>44867</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44867</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45324,7 +45324,7 @@
         <v>44872</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>44874</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>44874</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>44875</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44879</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44879</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44881</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44881</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44888</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>44889</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>44889</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>44889</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44889</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44890</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44890</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>44890</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>44893</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>44896</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>44896</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>44901</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>44903</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>44903</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>44909</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>44909</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>44911</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>44911</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>44914</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>44917</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>44917</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>44917</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>44917</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>44920</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>44923</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44923</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>44923</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>44928</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>44930</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>44935</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>44936</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>44938</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>44938</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>44939</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>44939</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44939</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>44939</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>44939</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>44939</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>44939</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>44939</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44939</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>44939</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>44939</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>44939</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49127,7 +49127,7 @@
         <v>44942</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44943</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44944</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44944</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>44944</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>44945</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>44954</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>44955</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49878,7 +49878,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>44957</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>44960</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>44960</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>44960</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>44960</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>44960</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>44960</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>44963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>44971</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>44972</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>44972</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44972</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>44972</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>44972</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50959,7 +50959,7 @@
         <v>44972</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>44972</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>44972</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>44972</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>44972</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>44972</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>44972</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>44973</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>44978</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>44977</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>44977</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>44977</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>44978</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51755,7 +51755,7 @@
         <v>44981</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>44984</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>44985</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>44985</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>44985</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>44985</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>44985</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>44985</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>44987</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>44993</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>44993</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>44993</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>44994</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>44994</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>44995</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>45000</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52697,7 +52697,7 @@
         <v>45000</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>45000</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>45021</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52873,7 +52873,7 @@
         <v>45043</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45042</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>45043</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45048</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45048</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>45048</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53225,7 +53225,7 @@
         <v>45051</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45054</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>45056</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         <v>45056</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53463,7 +53463,7 @@
         <v>45057</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53525,7 +53525,7 @@
         <v>45062</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45076</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45084</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45084</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45084</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>45087</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53887,7 +53887,7 @@
         <v>45089</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>45089</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54001,7 +54001,7 @@
         <v>45089</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45090</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54120,7 +54120,7 @@
         <v>45090</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>45092</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>45093</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45092</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54363,7 +54363,7 @@
         <v>45092</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54420,7 +54420,7 @@
         <v>45093</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>45093</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
         <v>45096</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>45096</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45098</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>45098</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54777,7 +54777,7 @@
         <v>45099</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>45103</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54901,7 +54901,7 @@
         <v>45104</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54963,7 +54963,7 @@
         <v>45104</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>45104</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         <v>45104</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55149,7 +55149,7 @@
         <v>45105</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45106</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>45107</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45112</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45112</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45113</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45113</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45113</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45115</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45115</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45117</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>45117</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45119</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>45119</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45119</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>45125</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56126,7 +56126,7 @@
         <v>45125</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45140</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56411,7 +56411,7 @@
         <v>45143</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45142</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45148</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45148</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56721,7 +56721,7 @@
         <v>45147</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>45147</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>45148</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>45147</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45148</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57031,7 +57031,7 @@
         <v>45148</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>45149</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57150,7 +57150,7 @@
         <v>45149</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>45149</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57336,7 +57336,7 @@
         <v>45150</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57398,7 +57398,7 @@
         <v>45150</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57460,7 +57460,7 @@
         <v>45150</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45150</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45150</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45150</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>45152</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57765,7 +57765,7 @@
         <v>45152</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57822,7 +57822,7 @@
         <v>45155</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>45154</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>45155</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58003,7 +58003,7 @@
         <v>45154</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58065,7 +58065,7 @@
         <v>45155</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>45155</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58179,7 +58179,7 @@
         <v>45156</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58236,7 +58236,7 @@
         <v>45158</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58293,7 +58293,7 @@
         <v>45159</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58350,7 +58350,7 @@
         <v>45161</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>45161</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45162</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58536,7 +58536,7 @@
         <v>45161</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -58593,7 +58593,7 @@
         <v>45163</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45166</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45170</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58774,7 +58774,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>45170</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>45171</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58955,7 +58955,7 @@
         <v>45171</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59017,7 +59017,7 @@
         <v>45171</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59079,7 +59079,7 @@
         <v>45171</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45171</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45171</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59265,7 +59265,7 @@
         <v>45170</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45173</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45177</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59446,7 +59446,7 @@
         <v>45177</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>45177</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>45186</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>45187</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>45187</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59741,7 +59741,7 @@
         <v>45188</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59803,7 +59803,7 @@
         <v>45187</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59865,7 +59865,7 @@
         <v>45188</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59922,7 +59922,7 @@
         <v>45189</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59984,7 +59984,7 @@
         <v>45189</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60046,7 +60046,7 @@
         <v>45190</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45190</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45190</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45194</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60398,7 +60398,7 @@
         <v>45194</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         <v>45195</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60517,7 +60517,7 @@
         <v>45195</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45196</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>45196</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60698,7 +60698,7 @@
         <v>45196</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60817,7 +60817,7 @@
         <v>45195</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45198</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60941,7 +60941,7 @@
         <v>45199</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>45199</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>45203</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45203</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61189,7 +61189,7 @@
         <v>45203</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61313,7 +61313,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>45205</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45205</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>45205</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45205</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61685,7 +61685,7 @@
         <v>45205</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>45207</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61809,7 +61809,7 @@
         <v>45207</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61871,7 +61871,7 @@
         <v>45207</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>45207</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61995,7 +61995,7 @@
         <v>45208</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>45209</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62114,7 +62114,7 @@
         <v>45210</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62171,7 +62171,7 @@
         <v>45212</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62233,7 +62233,7 @@
         <v>45212</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>45212</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         <v>45217</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>45217</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62481,7 +62481,7 @@
         <v>45217</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45217</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45217</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>45217</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45217</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45216</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62848,7 +62848,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62910,7 +62910,7 @@
         <v>45217</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45217</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>45218</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63096,7 +63096,7 @@
         <v>45222</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63158,7 +63158,7 @@
         <v>45223</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63220,7 +63220,7 @@
         <v>45224</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63282,7 +63282,7 @@
         <v>45225</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>45226</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63406,7 +63406,7 @@
         <v>45225</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63468,7 +63468,7 @@
         <v>45226</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63530,7 +63530,7 @@
         <v>45226</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>45226</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63654,7 +63654,7 @@
         <v>45226</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>45227</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45229</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45229</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63892,7 +63892,7 @@
         <v>45230</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -64006,7 +64006,7 @@
         <v>45232</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64063,7 +64063,7 @@
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64120,7 +64120,7 @@
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64234,7 +64234,7 @@
         <v>45232</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>45233</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64408,14 +64408,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 54983-2023</t>
+          <t>A 54984-2023</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
-        <v>45237</v>
+        <v>45236</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64433,7 +64433,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -64470,14 +64470,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 54984-2023</t>
+          <t>A 54983-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
-        <v>45236</v>
+        <v>45237</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64495,7 +64495,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -64539,7 +64539,7 @@
         <v>45237</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64601,7 +64601,7 @@
         <v>45236</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64656,14 +64656,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 55326-2023</t>
+          <t>A 55327-2023</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64681,7 +64681,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -64718,14 +64718,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 55327-2023</t>
+          <t>A 55335-2023</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64743,7 +64743,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -64780,14 +64780,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 55335-2023</t>
+          <t>A 55325-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
-        <v>45238</v>
+        <v>45237</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64805,7 +64805,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -64842,14 +64842,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 55325-2023</t>
+          <t>A 55326-2023</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64867,7 +64867,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -64911,7 +64911,7 @@
         <v>45238</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64961,14 +64961,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 56758-2023</t>
+          <t>A 56747-2023</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -64986,7 +64986,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>371.4</v>
+        <v>16.2</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -65023,14 +65023,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 56830-2023</t>
+          <t>A 56823-2023</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65048,7 +65048,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>66.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -65085,14 +65085,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 56747-2023</t>
+          <t>A 56847-2023</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65110,7 +65110,7 @@
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>16.2</v>
+        <v>41</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -65147,14 +65147,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 56754-2023</t>
+          <t>A 56758-2023</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65172,7 +65172,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>17.7</v>
+        <v>371.4</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -65209,14 +65209,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 56763-2023</t>
+          <t>A 56830-2023</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65234,7 +65234,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>78</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -65271,14 +65271,14 @@
     <row r="1005" ht="15" customHeight="1">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>A 56823-2023</t>
+          <t>A 56754-2023</t>
         </is>
       </c>
       <c r="B1005" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65296,7 +65296,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>81.40000000000001</v>
+        <v>17.7</v>
       </c>
       <c r="H1005" t="n">
         <v>0</v>
@@ -65333,14 +65333,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 56847-2023</t>
+          <t>A 56763-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65358,7 +65358,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -65395,14 +65395,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 57108-2023</t>
+          <t>A 57123-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65415,7 +65415,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>0.6</v>
+        <v>16.1</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -65459,7 +65459,7 @@
         <v>45239</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65509,14 +65509,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 57123-2023</t>
+          <t>A 57108-2023</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65529,7 +65529,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>16.1</v>
+        <v>0.6</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -65573,7 +65573,7 @@
         <v>45239</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>45240</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65680,14 +65680,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 56246-2023</t>
+          <t>A 56236-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65699,13 +65699,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1012" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1012" t="n">
-        <v>3.9</v>
+        <v>6.1</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -65742,14 +65737,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 56236-2023</t>
+          <t>A 56246-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65761,8 +65756,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1013" t="n">
-        <v>6.1</v>
+        <v>3.9</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -65806,7 +65806,7 @@
         <v>45240</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65868,7 +65868,7 @@
         <v>45243</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>45243</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65982,7 +65982,7 @@
         <v>45243</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -66039,7 +66039,7 @@
         <v>45244</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66096,7 +66096,7 @@
         <v>45244</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66153,7 +66153,7 @@
         <v>45245</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66210,7 +66210,7 @@
         <v>45247</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66272,7 +66272,7 @@
         <v>45248</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66329,7 +66329,7 @@
         <v>45251</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66384,14 +66384,14 @@
     <row r="1024" ht="15" customHeight="1">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>A 59110-2023</t>
+          <t>A 58756-2023</t>
         </is>
       </c>
       <c r="B1024" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66404,7 +66404,7 @@
         </is>
       </c>
       <c r="G1024" t="n">
-        <v>10.1</v>
+        <v>1.6</v>
       </c>
       <c r="H1024" t="n">
         <v>0</v>
@@ -66441,14 +66441,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 58749-2023</t>
+          <t>A 59117-2023</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66461,7 +66461,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -66498,14 +66498,14 @@
     <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>A 58756-2023</t>
+          <t>A 58749-2023</t>
         </is>
       </c>
       <c r="B1026" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66518,7 +66518,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -66555,14 +66555,14 @@
     <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 59117-2023</t>
+          <t>A 59110-2023</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66575,7 +66575,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>1</v>
+        <v>10.1</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -66619,7 +66619,7 @@
         <v>45252</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -66676,7 +66676,7 @@
         <v>45254</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66738,7 +66738,7 @@
         <v>45254</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66793,14 +66793,14 @@
     <row r="1031" ht="15" customHeight="1">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>A 60035-2023</t>
+          <t>A 59671-2023</t>
         </is>
       </c>
       <c r="B1031" s="1" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66812,8 +66812,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1031" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="H1031" t="n">
         <v>0</v>
@@ -66850,14 +66855,14 @@
     <row r="1032" ht="15" customHeight="1">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>A 59671-2023</t>
+          <t>A 60035-2023</t>
         </is>
       </c>
       <c r="B1032" s="1" t="n">
-        <v>45255</v>
+        <v>45254</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66869,13 +66874,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1032" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1032" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="H1032" t="n">
         <v>0</v>
@@ -66919,7 +66919,7 @@
         <v>45259</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66976,7 +66976,7 @@
         <v>45260</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67033,7 +67033,7 @@
         <v>45260</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -564,7 +564,7 @@
         <v>44350</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>44972</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44753</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44118</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44494</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>44412</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>44644</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>44838</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>44074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44350</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45125</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>44494</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>43741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45154</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44266</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>44645</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45119</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>43731</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>44263</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>44412</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45050</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>44964</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45181</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45201</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45030</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45030</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>44522</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>44972</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45205</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44838</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>45054</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45201</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>43805</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44095</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44474</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44838</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>44945</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45156</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45201</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44838</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>43336</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44095</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44266</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44838</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45119</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45201</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45201</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>43781</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44361</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45119</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45201</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45205</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>43731</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44678</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45201</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45205</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>43336</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43983</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44211</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45149</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>43381</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>43677</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44000</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44664</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45125</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>45132</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>44199</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>45205</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45208</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43608</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43726</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44609</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45050</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44000</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44206</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>43432</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>43987</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44039</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44382</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44420</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44732</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44972</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45113</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43523</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43658</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>43731</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>43923</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43924</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44235</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>44309</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>44401</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44518</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>44648</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44781</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45098</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>45112</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45125</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45233</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>43741</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>43775</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>43833</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>43837</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44141</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44195</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44476</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44494</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44531</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44532</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44560</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44638</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>44827</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>44852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44960</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44964</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44972</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44994</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45105</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>45166</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45240</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43332</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43332</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>43335</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>43340</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>43340</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>43347</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43350</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43360</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43370</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43370</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43370</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43375</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43375</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43377</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43377</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43377</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43377</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>43377</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43377</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43384</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43384</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43389</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>43389</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>43389</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>43395</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>43402</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>43409</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>43412</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>43412</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>43418</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43432</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>43432</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>43432</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>43432</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43440</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43444</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43448</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43451</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43467</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43472</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43472</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43475</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43476</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43476</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43479</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43480</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>43480</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>43480</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>43487</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>43496</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>43497</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>43500</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>43501</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>43503</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>43507</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>43509</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43509</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43509</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43509</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43523</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43523</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43523</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>43523</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>43542</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>43542</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>43542</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>43545</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>43545</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>43545</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>43558</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>43559</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>43559</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>43564</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>43592</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>43592</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>43594</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>43594</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>43608</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>43608</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>43612</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>43613</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>43614</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>43614</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>43640</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>43640</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>43640</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>43640</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>43640</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>43641</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>43648</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>43648</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>43656</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>43661</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43661</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>43664</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43664</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43664</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43665</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43682</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43690</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43699</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43700</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>43703</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>43705</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43712</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43714</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>43721</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>43726</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>43728</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>43731</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>43733</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>43733</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>43733</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>43739</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>43741</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>43746</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>43749</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>43749</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>43753</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>43755</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>43762</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>43762</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>43765</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>43774</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>43775</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>43791</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>43803</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>43805</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>43808</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>43810</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>43815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>43833</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>43833</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>43833</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>43837</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>43837</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>43838</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>43838</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>43854</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>43858</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>43858</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>43896</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>43896</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>43896</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>43896</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>43909</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>43910</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>43913</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>43913</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>43913</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>43913</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>43913</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>43913</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>43913</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>43913</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>43914</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>43915</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>43915</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>43915</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>43915</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>43923</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>43923</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>43923</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>43927</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>43935</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>43944</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>43945</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>43964</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>43964</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>43966</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>43966</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>43977</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>43983</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>43983</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>43986</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>43986</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44000</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>44000</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44007</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44007</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44022</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44032</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44036</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44039</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44060</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44064</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44064</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44069</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44071</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44075</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>44078</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44088</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44092</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44092</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44092</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>44092</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44092</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>44097</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>44105</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>44105</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44109</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44118</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>44129</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>44144</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44151</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44153</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44154</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44155</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44161</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44162</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44162</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>44165</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44169</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44172</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>44186</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>44186</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44193</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44195</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44208</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44211</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>44211</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44211</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>44216</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44216</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44235</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44235</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44235</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44235</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44235</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44235</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44235</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44237</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>44243</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>44246</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>44253</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>44253</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>44266</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44307</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44307</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44307</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44307</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44307</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44316</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44316</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44328</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44330</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44341</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44341</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44350</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44356</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44357</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44361</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44361</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44361</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44361</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44370</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44371</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44371</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44371</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44371</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44377</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44378</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>44382</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44386</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44389</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44389</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>44389</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44389</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44397</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44406</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44412</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44420</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>44420</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>44420</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44420</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>44420</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>44420</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44420</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>44419</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>44426</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>44433</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>44434</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44442</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44442</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44443</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44442</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>44452</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44452</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44452</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44452</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44452</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>44453</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44461</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44461</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>44462</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44469</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44470</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44473</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>44476</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>44476</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>44481</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>44482</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>44482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>44482</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44484</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44485</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44488</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44488</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44489</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44491</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44496</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44498</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44500</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>44502</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44503</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>44505</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>44511</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44515</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44515</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44515</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44522</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44522</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>44525</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44529</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>44531</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>44531</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44532</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44532</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44532</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44532</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>44533</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>44537</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44540</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44543</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44545</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44545</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44545</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44545</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>44545</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>44545</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44564</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>44567</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>44568</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>44578</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>44578</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>44594</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>44604</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>44609</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>44609</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>44615</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44615</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44617</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44617</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>44617</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>44617</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44617</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>44619</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44619</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44619</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44619</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44621</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44621</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44622</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44623</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44625</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44627</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44627</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44628</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44628</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44628</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44628</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44637</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44640</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         <v>44642</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>44657</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>44657</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>44658</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>44679</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44679</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44686</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44686</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44690</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44690</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>44692</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44693</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44693</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44698</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>44698</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>44700</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>44701</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>44708</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>44708</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44708</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44712</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>44713</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>44719</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>44726</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44725</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>44733</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38738,7 +38738,7 @@
         <v>44735</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>44735</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>44735</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44735</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>44741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44743</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44743</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>44743</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>44743</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44743</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>44743</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44743</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44743</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44743</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>44743</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44744</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>44744</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>44744</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44744</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>44744</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>44744</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44747</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>44747</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44748</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>44748</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>44754</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>44755</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>44756</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>44756</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>44757</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>44757</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>44757</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>44757</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>44773</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>44784</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>44784</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>44788</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44788</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>44788</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>44789</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44790</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>44797</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>44797</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41369,7 +41369,7 @@
         <v>44799</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>44798</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44799</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44799</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>44799</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44803</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>44802</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44802</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>44803</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44806</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>44805</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>44805</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44806</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>44810</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>44810</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>44813</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>44812</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44813</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44813</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44817</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44824</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>44824</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>44826</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>44827</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>44827</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>44826</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>44832</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>44831</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43204,7 +43204,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44834</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>44837</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>44837</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>44844</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>44847</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>44847</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>44847</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>44847</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>44847</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>44852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>44853</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>44852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>44853</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>44853</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>44852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>44853</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>44853</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>44855</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>44857</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>44859</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>44859</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>44858</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>44859</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44859</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>44858</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44859</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>44859</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>44859</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>44859</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>44862</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>44867</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44867</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45324,7 +45324,7 @@
         <v>44872</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>44874</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>44874</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>44875</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44879</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44879</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44881</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44881</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44888</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>44889</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>44889</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>44889</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44889</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44890</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44890</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>44890</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>44893</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>44896</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>44896</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>44901</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>44903</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>44903</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>44909</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>44909</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>44911</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>44911</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>44914</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>44917</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>44917</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>44917</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>44917</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>44920</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>44923</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44923</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>44923</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>44928</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>44930</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>44935</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>44936</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>44938</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>44938</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>44939</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>44939</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44939</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>44939</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>44939</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>44939</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>44939</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>44939</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44939</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>44939</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>44939</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>44939</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49127,7 +49127,7 @@
         <v>44942</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44943</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44944</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44944</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>44944</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>44945</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>44954</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>44955</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49878,7 +49878,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>44957</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>44960</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>44960</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>44960</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>44960</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>44960</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>44960</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>44963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>44971</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>44972</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>44972</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44972</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>44972</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>44972</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50959,7 +50959,7 @@
         <v>44972</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>44972</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>44972</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>44972</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>44972</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>44972</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>44972</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>44973</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>44978</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>44977</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>44977</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>44977</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>44978</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51755,7 +51755,7 @@
         <v>44981</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>44984</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>44985</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>44985</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>44985</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>44985</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>44985</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>44985</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>44987</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>44993</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>44993</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>44993</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>44994</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>44994</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>44995</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>45000</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52697,7 +52697,7 @@
         <v>45000</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>45000</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>45021</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52873,7 +52873,7 @@
         <v>45043</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45042</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>45043</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45048</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45048</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>45048</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53225,7 +53225,7 @@
         <v>45051</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45054</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>45056</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         <v>45056</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53463,7 +53463,7 @@
         <v>45057</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53525,7 +53525,7 @@
         <v>45062</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45076</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45084</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45084</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45084</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>45087</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53887,7 +53887,7 @@
         <v>45089</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>45089</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54001,7 +54001,7 @@
         <v>45089</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45090</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54120,7 +54120,7 @@
         <v>45090</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>45092</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>45093</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45092</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54363,7 +54363,7 @@
         <v>45092</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54420,7 +54420,7 @@
         <v>45093</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>45093</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
         <v>45096</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>45096</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45098</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>45098</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54777,7 +54777,7 @@
         <v>45099</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>45103</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54901,7 +54901,7 @@
         <v>45104</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54963,7 +54963,7 @@
         <v>45104</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>45104</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         <v>45104</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55149,7 +55149,7 @@
         <v>45105</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45106</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>45107</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45112</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45112</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45113</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45113</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45113</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45115</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45115</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45117</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>45117</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45119</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>45119</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45119</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>45125</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56126,7 +56126,7 @@
         <v>45125</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45140</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56411,7 +56411,7 @@
         <v>45143</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45142</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45148</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45148</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56721,7 +56721,7 @@
         <v>45147</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>45147</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>45148</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>45147</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45148</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57031,7 +57031,7 @@
         <v>45148</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>45149</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57150,7 +57150,7 @@
         <v>45149</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>45149</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57336,7 +57336,7 @@
         <v>45150</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57398,7 +57398,7 @@
         <v>45150</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57460,7 +57460,7 @@
         <v>45150</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45150</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45150</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45150</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>45152</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57765,7 +57765,7 @@
         <v>45152</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57822,7 +57822,7 @@
         <v>45155</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>45154</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>45155</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58003,7 +58003,7 @@
         <v>45154</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58065,7 +58065,7 @@
         <v>45155</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>45155</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58179,7 +58179,7 @@
         <v>45156</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58236,7 +58236,7 @@
         <v>45158</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58293,7 +58293,7 @@
         <v>45159</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58350,7 +58350,7 @@
         <v>45161</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>45161</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45162</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58536,7 +58536,7 @@
         <v>45161</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -58593,7 +58593,7 @@
         <v>45163</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45166</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45170</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58774,7 +58774,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>45170</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>45171</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58955,7 +58955,7 @@
         <v>45171</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59017,7 +59017,7 @@
         <v>45171</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59079,7 +59079,7 @@
         <v>45171</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45171</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45171</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59265,7 +59265,7 @@
         <v>45170</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45173</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45177</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59446,7 +59446,7 @@
         <v>45177</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>45177</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>45186</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>45187</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>45187</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59741,7 +59741,7 @@
         <v>45188</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59803,7 +59803,7 @@
         <v>45187</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59865,7 +59865,7 @@
         <v>45188</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59922,7 +59922,7 @@
         <v>45189</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59984,7 +59984,7 @@
         <v>45189</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60046,7 +60046,7 @@
         <v>45190</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45190</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45190</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45194</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60398,7 +60398,7 @@
         <v>45194</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         <v>45195</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60517,7 +60517,7 @@
         <v>45195</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45196</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>45196</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60698,7 +60698,7 @@
         <v>45196</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60817,7 +60817,7 @@
         <v>45195</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45198</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60941,7 +60941,7 @@
         <v>45199</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>45199</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>45203</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45203</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61189,7 +61189,7 @@
         <v>45203</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61313,7 +61313,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>45205</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45205</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>45205</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45205</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61685,7 +61685,7 @@
         <v>45205</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>45207</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61809,7 +61809,7 @@
         <v>45207</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61871,7 +61871,7 @@
         <v>45207</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>45207</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61995,7 +61995,7 @@
         <v>45208</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>45209</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62114,7 +62114,7 @@
         <v>45210</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62171,7 +62171,7 @@
         <v>45212</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62233,7 +62233,7 @@
         <v>45212</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>45212</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         <v>45217</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>45217</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62481,7 +62481,7 @@
         <v>45217</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45217</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45217</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>45217</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45217</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45216</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62848,7 +62848,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62910,7 +62910,7 @@
         <v>45217</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45217</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>45218</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63096,7 +63096,7 @@
         <v>45222</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63158,7 +63158,7 @@
         <v>45223</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63220,7 +63220,7 @@
         <v>45224</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63282,7 +63282,7 @@
         <v>45225</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>45226</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63406,7 +63406,7 @@
         <v>45225</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63468,7 +63468,7 @@
         <v>45226</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63530,7 +63530,7 @@
         <v>45226</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>45226</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63654,7 +63654,7 @@
         <v>45226</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>45227</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45229</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45229</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63892,7 +63892,7 @@
         <v>45230</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -64006,7 +64006,7 @@
         <v>45232</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64063,7 +64063,7 @@
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64120,7 +64120,7 @@
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64234,7 +64234,7 @@
         <v>45232</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>45233</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64346,14 +64346,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 54733-2023</t>
+          <t>A 54983-2023</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
-        <v>45236</v>
+        <v>45237</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64367,11 +64367,11 @@
       </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="G990" t="n">
-        <v>7.1</v>
+        <v>1.9</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -64408,14 +64408,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 54984-2023</t>
+          <t>A 54733-2023</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64429,11 +64429,11 @@
       </c>
       <c r="F991" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="G991" t="n">
-        <v>2.4</v>
+        <v>7.1</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -64470,14 +64470,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 54983-2023</t>
+          <t>A 54984-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
-        <v>45237</v>
+        <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64495,7 +64495,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -64539,7 +64539,7 @@
         <v>45237</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64601,7 +64601,7 @@
         <v>45236</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>45238</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64725,7 +64725,7 @@
         <v>45238</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64787,7 +64787,7 @@
         <v>45237</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64849,7 +64849,7 @@
         <v>45238</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64904,14 +64904,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 55643-2023</t>
+          <t>A 56758-2023</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64923,8 +64923,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="G999" t="n">
-        <v>23.1</v>
+        <v>371.4</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -64961,14 +64966,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 56747-2023</t>
+          <t>A 56830-2023</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -64986,7 +64991,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>16.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -65023,14 +65028,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 56823-2023</t>
+          <t>A 56754-2023</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65048,7 +65053,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>81.40000000000001</v>
+        <v>17.7</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -65085,14 +65090,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 56847-2023</t>
+          <t>A 56763-2023</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65110,7 +65115,7 @@
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -65147,14 +65152,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 56758-2023</t>
+          <t>A 55643-2023</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65166,13 +65171,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1003" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="G1003" t="n">
-        <v>371.4</v>
+        <v>23.1</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -65209,14 +65209,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 56830-2023</t>
+          <t>A 56747-2023</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65234,7 +65234,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>66.90000000000001</v>
+        <v>16.2</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -65271,14 +65271,14 @@
     <row r="1005" ht="15" customHeight="1">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>A 56754-2023</t>
+          <t>A 56847-2023</t>
         </is>
       </c>
       <c r="B1005" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65296,7 +65296,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>17.7</v>
+        <v>41</v>
       </c>
       <c r="H1005" t="n">
         <v>0</v>
@@ -65333,14 +65333,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 56763-2023</t>
+          <t>A 56823-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65358,7 +65358,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>78</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -65395,14 +65395,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 57123-2023</t>
+          <t>A 57108-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65415,7 +65415,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>16.1</v>
+        <v>0.6</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -65452,14 +65452,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 57246-2023</t>
+          <t>A 57123-2023</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65472,7 +65472,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>15.3</v>
+        <v>16.1</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -65509,14 +65509,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 57108-2023</t>
+          <t>A 57246-2023</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65529,7 +65529,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>0.6</v>
+        <v>15.3</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -65573,7 +65573,7 @@
         <v>45239</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65623,14 +65623,14 @@
     <row r="1011" ht="15" customHeight="1">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>A 56235-2023</t>
+          <t>A 56245-2023</t>
         </is>
       </c>
       <c r="B1011" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65642,8 +65642,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1011" t="n">
-        <v>12.7</v>
+        <v>1.1</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -65680,14 +65685,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 56236-2023</t>
+          <t>A 56246-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65699,8 +65704,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1012" t="n">
-        <v>6.1</v>
+        <v>3.9</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -65737,14 +65747,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 56246-2023</t>
+          <t>A 56236-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65756,13 +65766,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1013" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1013" t="n">
-        <v>3.9</v>
+        <v>6.1</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -65799,14 +65804,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 56245-2023</t>
+          <t>A 56235-2023</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65818,13 +65823,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1014" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1014" t="n">
-        <v>1.1</v>
+        <v>12.7</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -65868,7 +65868,7 @@
         <v>45243</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>45243</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65982,7 +65982,7 @@
         <v>45243</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -66039,7 +66039,7 @@
         <v>45244</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66096,7 +66096,7 @@
         <v>45244</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66153,7 +66153,7 @@
         <v>45245</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66210,7 +66210,7 @@
         <v>45247</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66272,7 +66272,7 @@
         <v>45248</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66329,7 +66329,7 @@
         <v>45251</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66391,7 +66391,7 @@
         <v>45251</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66448,7 +66448,7 @@
         <v>45251</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66505,7 +66505,7 @@
         <v>45251</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66562,7 +66562,7 @@
         <v>45251</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66619,7 +66619,7 @@
         <v>45252</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -66669,14 +66669,14 @@
     <row r="1029" ht="15" customHeight="1">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>A 59664-2023</t>
+          <t>A 59663-2023</t>
         </is>
       </c>
       <c r="B1029" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66694,7 +66694,7 @@
         </is>
       </c>
       <c r="G1029" t="n">
-        <v>3.3</v>
+        <v>12.8</v>
       </c>
       <c r="H1029" t="n">
         <v>0</v>
@@ -66731,14 +66731,14 @@
     <row r="1030" ht="15" customHeight="1">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>A 59663-2023</t>
+          <t>A 59671-2023</t>
         </is>
       </c>
       <c r="B1030" s="1" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66756,7 +66756,7 @@
         </is>
       </c>
       <c r="G1030" t="n">
-        <v>12.8</v>
+        <v>1.3</v>
       </c>
       <c r="H1030" t="n">
         <v>0</v>
@@ -66793,14 +66793,14 @@
     <row r="1031" ht="15" customHeight="1">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>A 59671-2023</t>
+          <t>A 60035-2023</t>
         </is>
       </c>
       <c r="B1031" s="1" t="n">
-        <v>45255</v>
+        <v>45254</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66812,13 +66812,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1031" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1031" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="H1031" t="n">
         <v>0</v>
@@ -66855,14 +66850,14 @@
     <row r="1032" ht="15" customHeight="1">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>A 60035-2023</t>
+          <t>A 59664-2023</t>
         </is>
       </c>
       <c r="B1032" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66874,8 +66869,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1032" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="H1032" t="n">
         <v>0</v>
@@ -66919,7 +66919,7 @@
         <v>45259</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66976,7 +66976,7 @@
         <v>45260</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67033,7 +67033,7 @@
         <v>45260</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -564,7 +564,7 @@
         <v>44350</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>44972</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44753</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44118</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44494</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>44412</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>44644</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>44838</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>44074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44350</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45125</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>44494</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>43741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45154</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44266</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>44645</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45119</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>43731</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>44263</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>44412</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45050</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>44964</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45181</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45201</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45030</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45030</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>44522</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>44972</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45205</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44838</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>45054</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45201</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>43805</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44095</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44474</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44838</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>44945</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45156</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45201</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44838</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>43336</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44095</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44266</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44838</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45119</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45201</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45201</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>43781</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44361</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45119</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45201</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45205</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>43731</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44678</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45201</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45205</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>43336</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43983</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44211</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45149</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>43381</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>43677</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44000</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44664</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45125</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>45132</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>44199</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>45205</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45208</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43608</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43726</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44609</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45050</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44000</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44206</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>43432</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>43987</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44039</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44382</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44420</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44732</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44972</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45113</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43523</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43658</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>43731</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>43923</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43924</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44235</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>44309</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>44401</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44518</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>44648</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44781</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45098</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>45112</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45125</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45233</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>43741</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>43775</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>43833</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>43837</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44141</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44195</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44476</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44494</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44531</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44532</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44560</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44638</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>44827</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>44852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44960</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44964</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44972</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44994</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45105</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>45166</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45240</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43332</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43332</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>43335</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>43340</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>43340</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>43347</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43350</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43360</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43370</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43370</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43370</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43375</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43375</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43377</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43377</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43377</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43377</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>43377</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43377</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43384</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43384</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43389</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>43389</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>43389</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>43395</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>43402</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>43409</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>43412</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>43412</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>43418</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43432</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>43432</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>43432</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>43432</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43440</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43444</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43448</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43451</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43467</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43472</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43472</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43475</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43476</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43476</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43479</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43480</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>43480</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>43480</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>43487</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>43496</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>43497</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>43500</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>43501</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>43503</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>43507</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>43509</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43509</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43509</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43509</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43523</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43523</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43523</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>43523</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>43542</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>43542</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>43542</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>43545</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>43545</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>43545</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>43558</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>43559</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>43559</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>43564</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>43592</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>43592</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>43594</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>43594</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>43608</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>43608</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>43612</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>43613</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>43614</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>43614</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>43640</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>43640</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>43640</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>43640</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>43640</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>43641</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>43648</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>43648</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>43656</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>43661</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43661</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>43664</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43664</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43664</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43665</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43682</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43690</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43699</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43700</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>43703</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>43705</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43712</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43714</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>43721</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>43726</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>43728</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>43731</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>43733</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>43733</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>43733</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>43739</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>43741</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>43746</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>43749</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>43749</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>43753</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>43755</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>43762</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>43762</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>43765</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>43774</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>43775</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>43791</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>43803</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>43805</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>43808</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>43810</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>43815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>43833</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>43833</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>43833</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>43837</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>43837</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>43838</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>43838</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>43854</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>43858</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>43858</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>43896</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>43896</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>43896</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>43896</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>43909</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>43910</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>43913</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>43913</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>43913</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>43913</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>43913</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>43913</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>43913</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>43913</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>43914</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>43915</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>43915</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>43915</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>43915</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>43923</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>43923</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>43923</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>43927</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>43935</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>43944</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>43945</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>43964</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>43964</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>43966</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>43966</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>43977</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>43983</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>43983</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>43986</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>43986</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44000</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>44000</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44007</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44007</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44022</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44032</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44036</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44039</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44060</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44064</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44064</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44069</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44071</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44075</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>44078</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44088</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44092</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44092</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44092</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>44092</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44092</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>44097</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>44105</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>44105</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44109</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44118</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>44129</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>44144</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44151</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44153</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44154</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44155</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44161</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44162</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44162</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>44165</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44169</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44172</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>44186</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>44186</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44193</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44195</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44208</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44211</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>44211</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44211</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>44216</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44216</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44235</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44235</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44235</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44235</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44235</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44235</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44235</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44237</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>44243</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>44246</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>44253</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>44253</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>44266</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44307</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44307</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44307</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44307</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44307</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44316</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44316</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44328</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44330</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44341</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44341</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44350</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44356</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44357</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44361</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44361</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44361</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44361</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44370</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44371</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44371</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44371</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44371</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44377</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44378</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>44382</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44386</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44389</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44389</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>44389</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44389</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44397</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44406</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44412</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44420</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>44420</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>44420</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44420</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>44420</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>44420</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44420</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>44419</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>44426</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>44433</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>44434</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44442</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44442</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44443</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44442</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>44452</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44452</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44452</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44452</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44452</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>44453</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44461</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44461</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>44462</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44469</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44470</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44473</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>44476</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>44476</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>44481</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>44482</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>44482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>44482</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44484</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44485</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44488</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44488</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44489</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44491</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44496</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44498</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44500</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>44502</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44503</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>44505</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>44511</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44515</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44515</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44515</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44522</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44522</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>44525</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44529</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>44531</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>44531</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44532</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44532</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44532</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44532</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>44533</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>44537</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44540</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44543</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44545</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44545</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44545</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44545</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>44545</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>44545</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44564</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>44567</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>44568</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>44578</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>44578</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>44594</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>44604</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>44609</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>44609</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>44615</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44615</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44617</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44617</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>44617</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>44617</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44617</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>44619</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44619</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44619</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44619</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44621</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44621</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44622</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44623</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44625</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44627</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44627</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44628</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44628</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44628</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44628</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44637</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44640</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         <v>44642</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>44657</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>44657</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>44658</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>44679</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44679</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44686</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44686</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44690</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44690</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>44692</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44693</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44693</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44698</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>44698</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>44700</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>44701</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>44708</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>44708</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44708</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44712</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>44713</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>44719</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>44726</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44725</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>44733</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38738,7 +38738,7 @@
         <v>44735</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>44735</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>44735</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44735</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>44741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44743</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44743</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>44743</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>44743</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44743</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>44743</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44743</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44743</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44743</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>44743</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44744</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>44744</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>44744</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44744</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>44744</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>44744</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44747</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>44747</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44748</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>44748</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>44754</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>44755</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>44756</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>44756</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>44757</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>44757</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>44757</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>44757</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>44773</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>44784</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>44784</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>44788</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44788</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>44788</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>44789</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44790</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>44797</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>44797</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41369,7 +41369,7 @@
         <v>44799</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>44798</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44799</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44799</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>44799</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44803</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>44802</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44802</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>44803</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44806</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>44805</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>44805</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44806</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>44810</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>44810</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>44813</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>44812</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44813</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44813</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44817</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44824</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>44824</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>44826</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>44827</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>44827</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>44826</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>44832</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>44831</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43204,7 +43204,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44834</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>44837</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>44837</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>44844</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>44847</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>44847</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>44847</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>44847</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>44847</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>44852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>44853</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>44852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>44853</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>44853</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>44852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>44853</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>44853</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>44855</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>44857</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>44859</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>44859</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>44858</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>44859</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44859</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>44858</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44859</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>44859</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>44859</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>44859</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>44862</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>44867</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44867</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45324,7 +45324,7 @@
         <v>44872</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>44874</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>44874</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>44875</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44879</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44879</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44881</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44881</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44888</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>44889</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>44889</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>44889</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44889</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44890</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44890</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>44890</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>44893</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>44896</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>44896</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>44901</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>44903</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>44903</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>44909</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>44909</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>44911</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>44911</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>44914</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>44917</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>44917</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>44917</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>44917</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>44920</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>44923</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44923</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>44923</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>44928</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>44930</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>44935</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>44936</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>44938</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>44938</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>44939</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>44939</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44939</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>44939</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>44939</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>44939</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>44939</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>44939</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44939</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>44939</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>44939</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>44939</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49127,7 +49127,7 @@
         <v>44942</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44943</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44944</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44944</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>44944</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>44945</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>44954</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>44955</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49878,7 +49878,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>44957</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>44960</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>44960</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>44960</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>44960</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>44960</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>44960</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>44963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>44971</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>44972</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>44972</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44972</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>44972</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>44972</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50959,7 +50959,7 @@
         <v>44972</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>44972</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>44972</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>44972</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>44972</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>44972</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>44972</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>44973</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>44978</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>44977</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>44977</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>44977</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>44978</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51755,7 +51755,7 @@
         <v>44981</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>44984</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>44985</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>44985</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>44985</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>44985</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>44985</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>44985</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>44987</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>44993</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>44993</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>44993</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>44994</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>44994</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>44995</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>45000</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52697,7 +52697,7 @@
         <v>45000</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>45000</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>45021</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52873,7 +52873,7 @@
         <v>45043</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45042</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>45043</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45048</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45048</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>45048</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53225,7 +53225,7 @@
         <v>45051</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45054</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>45056</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         <v>45056</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53463,7 +53463,7 @@
         <v>45057</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53525,7 +53525,7 @@
         <v>45062</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45076</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45084</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45084</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45084</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>45087</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53887,7 +53887,7 @@
         <v>45089</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>45089</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54001,7 +54001,7 @@
         <v>45089</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45090</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54120,7 +54120,7 @@
         <v>45090</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>45092</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>45093</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45092</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54363,7 +54363,7 @@
         <v>45092</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54420,7 +54420,7 @@
         <v>45093</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>45093</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
         <v>45096</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>45096</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45098</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>45098</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54777,7 +54777,7 @@
         <v>45099</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>45103</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54901,7 +54901,7 @@
         <v>45104</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54963,7 +54963,7 @@
         <v>45104</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>45104</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         <v>45104</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55149,7 +55149,7 @@
         <v>45105</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45106</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>45107</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45112</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45112</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45113</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45113</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45113</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45115</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45115</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45117</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>45117</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45119</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>45119</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45119</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>45125</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56126,7 +56126,7 @@
         <v>45125</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45140</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56411,7 +56411,7 @@
         <v>45143</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45142</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45148</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45148</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56721,7 +56721,7 @@
         <v>45147</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>45147</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>45148</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>45147</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45148</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57031,7 +57031,7 @@
         <v>45148</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>45149</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57150,7 +57150,7 @@
         <v>45149</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>45149</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57336,7 +57336,7 @@
         <v>45150</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57398,7 +57398,7 @@
         <v>45150</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57460,7 +57460,7 @@
         <v>45150</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45150</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45150</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45150</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>45152</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57765,7 +57765,7 @@
         <v>45152</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57822,7 +57822,7 @@
         <v>45155</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>45154</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>45155</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58003,7 +58003,7 @@
         <v>45154</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58065,7 +58065,7 @@
         <v>45155</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>45155</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58179,7 +58179,7 @@
         <v>45156</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58236,7 +58236,7 @@
         <v>45158</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58293,7 +58293,7 @@
         <v>45159</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58350,7 +58350,7 @@
         <v>45161</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>45161</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45162</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58536,7 +58536,7 @@
         <v>45161</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -58593,7 +58593,7 @@
         <v>45163</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45166</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45170</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58774,7 +58774,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>45170</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>45171</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58955,7 +58955,7 @@
         <v>45171</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59017,7 +59017,7 @@
         <v>45171</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59079,7 +59079,7 @@
         <v>45171</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45171</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45171</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59265,7 +59265,7 @@
         <v>45170</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45173</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45177</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59446,7 +59446,7 @@
         <v>45177</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>45177</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>45186</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>45187</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>45187</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59741,7 +59741,7 @@
         <v>45188</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59803,7 +59803,7 @@
         <v>45187</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59865,7 +59865,7 @@
         <v>45188</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59922,7 +59922,7 @@
         <v>45189</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59984,7 +59984,7 @@
         <v>45189</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60046,7 +60046,7 @@
         <v>45190</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45190</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45190</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45194</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60398,7 +60398,7 @@
         <v>45194</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         <v>45195</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60517,7 +60517,7 @@
         <v>45195</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45196</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>45196</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60698,7 +60698,7 @@
         <v>45196</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60817,7 +60817,7 @@
         <v>45195</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45198</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60941,7 +60941,7 @@
         <v>45199</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>45199</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>45203</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45203</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61189,7 +61189,7 @@
         <v>45203</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61313,7 +61313,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>45205</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45205</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>45205</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45205</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61685,7 +61685,7 @@
         <v>45205</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>45207</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61809,7 +61809,7 @@
         <v>45207</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61871,7 +61871,7 @@
         <v>45207</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>45207</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61995,7 +61995,7 @@
         <v>45208</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>45209</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62114,7 +62114,7 @@
         <v>45210</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62171,7 +62171,7 @@
         <v>45212</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62233,7 +62233,7 @@
         <v>45212</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>45212</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         <v>45217</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>45217</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62481,7 +62481,7 @@
         <v>45217</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45217</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45217</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>45217</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45217</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45216</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62848,7 +62848,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62910,7 +62910,7 @@
         <v>45217</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45217</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>45218</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63096,7 +63096,7 @@
         <v>45222</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63158,7 +63158,7 @@
         <v>45223</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63220,7 +63220,7 @@
         <v>45224</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63282,7 +63282,7 @@
         <v>45225</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>45226</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63406,7 +63406,7 @@
         <v>45225</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63468,7 +63468,7 @@
         <v>45226</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63530,7 +63530,7 @@
         <v>45226</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>45226</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63654,7 +63654,7 @@
         <v>45226</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>45227</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45229</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45229</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63892,7 +63892,7 @@
         <v>45230</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -64006,7 +64006,7 @@
         <v>45232</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64063,7 +64063,7 @@
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64120,7 +64120,7 @@
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64234,7 +64234,7 @@
         <v>45232</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>45233</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64415,7 +64415,7 @@
         <v>45237</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64539,7 +64539,7 @@
         <v>45237</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64601,7 +64601,7 @@
         <v>45236</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>45237</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64725,7 +64725,7 @@
         <v>45238</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64787,7 +64787,7 @@
         <v>45238</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64849,7 +64849,7 @@
         <v>45238</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64911,7 +64911,7 @@
         <v>45238</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64973,7 +64973,7 @@
         <v>45238</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -65035,7 +65035,7 @@
         <v>45238</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65097,7 +65097,7 @@
         <v>45238</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>45238</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65221,7 +65221,7 @@
         <v>45238</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65283,7 +65283,7 @@
         <v>45238</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65340,7 +65340,7 @@
         <v>45238</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65395,14 +65395,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 57108-2023</t>
+          <t>A 57137-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65415,7 +65415,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>0.6</v>
+        <v>38.8</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -65452,14 +65452,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 57137-2023</t>
+          <t>A 57108-2023</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65472,7 +65472,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>38.8</v>
+        <v>0.6</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -65516,7 +65516,7 @@
         <v>45239</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65573,7 +65573,7 @@
         <v>45239</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>45239</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65680,14 +65680,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 56236-2023</t>
+          <t>A 56246-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65699,8 +65699,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1012" t="n">
-        <v>6.1</v>
+        <v>3.9</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -65737,14 +65742,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 56246-2023</t>
+          <t>A 56245-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65762,7 +65767,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -65799,14 +65804,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 56245-2023</t>
+          <t>A 56235-2023</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65818,13 +65823,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1014" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1014" t="n">
-        <v>1.1</v>
+        <v>12.7</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -65861,14 +65861,14 @@
     <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 56235-2023</t>
+          <t>A 56236-2023</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65881,7 +65881,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>12.7</v>
+        <v>6.1</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -65918,14 +65918,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 56617-2023</t>
+          <t>A 57691-2023</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65938,7 +65938,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -65975,14 +65975,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 56622-2023</t>
+          <t>A 56617-2023</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -65995,7 +65995,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -66032,14 +66032,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 57691-2023</t>
+          <t>A 56622-2023</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66052,7 +66052,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -66089,14 +66089,14 @@
     <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>A 57057-2023</t>
+          <t>A 57058-2023</t>
         </is>
       </c>
       <c r="B1019" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66109,7 +66109,7 @@
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -66146,14 +66146,14 @@
     <row r="1020" ht="15" customHeight="1">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>A 57058-2023</t>
+          <t>A 57057-2023</t>
         </is>
       </c>
       <c r="B1020" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66166,7 +66166,7 @@
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="H1020" t="n">
         <v>0</v>
@@ -66210,7 +66210,7 @@
         <v>45245</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66267,7 +66267,7 @@
         <v>45247</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66329,7 +66329,7 @@
         <v>45248</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66386,7 +66386,7 @@
         <v>45251</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66441,14 +66441,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 58756-2023</t>
+          <t>A 58749-2023</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66461,7 +66461,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -66498,14 +66498,14 @@
     <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>A 59117-2023</t>
+          <t>A 58756-2023</t>
         </is>
       </c>
       <c r="B1026" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66518,7 +66518,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -66555,14 +66555,14 @@
     <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 58749-2023</t>
+          <t>A 59117-2023</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66575,7 +66575,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -66619,7 +66619,7 @@
         <v>45251</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -66676,7 +66676,7 @@
         <v>45252</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66726,14 +66726,14 @@
     <row r="1030" ht="15" customHeight="1">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>A 59664-2023</t>
+          <t>A 60035-2023</t>
         </is>
       </c>
       <c r="B1030" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66745,13 +66745,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1030" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1030" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="H1030" t="n">
         <v>0</v>
@@ -66795,7 +66790,7 @@
         <v>45254</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66857,7 +66852,7 @@
         <v>45255</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66912,14 +66907,14 @@
     <row r="1033" ht="15" customHeight="1">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>A 60035-2023</t>
+          <t>A 59664-2023</t>
         </is>
       </c>
       <c r="B1033" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66931,8 +66926,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1033" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="H1033" t="n">
         <v>0</v>
@@ -66976,7 +66976,7 @@
         <v>45259</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67033,7 +67033,7 @@
         <v>45260</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -67090,7 +67090,7 @@
         <v>45260</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -67140,14 +67140,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 61780-2023</t>
+          <t>A 61779-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -67165,7 +67165,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -67202,14 +67202,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 61779-2023</t>
+          <t>A 62021-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -67221,13 +67221,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1038" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1038" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -67271,7 +67266,7 @@
         <v>45265</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -67326,14 +67321,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 61973-2023</t>
+          <t>A 61778-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -67345,8 +67340,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1040" t="n">
-        <v>24.9</v>
+        <v>3.9</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -67383,14 +67383,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 62021-2023</t>
+          <t>A 61973-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -67403,7 +67403,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>2.4</v>
+        <v>24.9</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -67440,14 +67440,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 61778-2023</t>
+          <t>A 62015-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -67459,13 +67459,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1042" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1042" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -67502,14 +67497,14 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 62015-2023</t>
+          <t>A 61780-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -67521,8 +67516,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1043" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -564,7 +564,7 @@
         <v>44350</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>44972</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44753</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44118</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44494</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>44412</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>44644</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>44838</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>44074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44350</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45125</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>44494</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>43741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45154</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44266</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>44645</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45119</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>43731</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>44263</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>44412</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45050</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>44964</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45181</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45201</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45030</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45030</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>44522</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>44972</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45205</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44838</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>45054</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45201</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>43805</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44095</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44474</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44838</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>44945</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45156</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45201</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44838</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>43336</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44095</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44266</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44838</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45119</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45201</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45201</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>43781</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44361</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45119</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45201</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45205</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>43731</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44678</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45201</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45205</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>43336</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43983</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44211</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45149</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>43381</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>43677</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44000</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44664</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45125</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>45132</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>44199</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>45205</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45208</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43608</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43726</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44609</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45050</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44000</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44206</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>43432</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>43987</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44039</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44382</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44420</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44732</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44972</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45113</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43523</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43658</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>43731</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>43923</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43924</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44235</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>44309</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>44401</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44518</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>44648</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44781</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45098</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>45112</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45125</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45233</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>43741</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>43775</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>43833</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>43837</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44141</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44195</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44476</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44494</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44531</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44532</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44560</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44638</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>44827</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>44852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44960</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44964</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44972</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44994</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45105</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>45166</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45240</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43332</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43332</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>43335</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>43340</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>43340</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>43347</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43350</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43360</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43370</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43370</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43370</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43375</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43375</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43377</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43377</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43377</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43377</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>43377</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43377</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43384</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43384</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43389</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>43389</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>43389</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>43395</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>43402</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>43409</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>43412</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>43412</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>43418</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43432</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>43432</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>43432</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>43432</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43440</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43444</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43448</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43451</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43467</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43472</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43472</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43475</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43476</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43476</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43479</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43480</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>43480</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>43480</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>43487</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>43496</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>43497</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>43500</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>43501</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>43503</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>43507</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>43509</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43509</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43509</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43509</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43523</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43523</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43523</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>43523</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>43542</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>43542</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>43542</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>43545</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>43545</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>43545</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>43558</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>43559</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>43559</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>43564</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>43592</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>43592</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>43594</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>43594</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>43608</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>43608</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>43612</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>43613</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>43614</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>43614</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>43640</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>43640</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>43640</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>43640</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>43640</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>43641</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>43648</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>43648</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>43656</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>43661</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43661</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>43664</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43664</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43664</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43665</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43682</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43690</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43699</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43700</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>43703</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>43705</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43712</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43714</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>43721</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>43726</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>43728</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>43731</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>43733</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>43733</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>43733</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>43739</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>43741</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>43746</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>43749</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>43749</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>43753</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>43755</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>43762</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>43762</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>43765</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>43774</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>43775</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>43791</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>43803</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>43805</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>43808</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>43810</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>43815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>43833</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>43833</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>43833</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>43837</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>43837</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>43838</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>43838</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>43854</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>43858</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>43858</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>43896</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>43896</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>43896</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>43896</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>43909</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>43910</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>43913</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>43913</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>43913</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>43913</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>43913</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>43913</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>43913</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>43913</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>43914</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>43915</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>43915</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>43915</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>43915</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>43923</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>43923</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>43923</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>43927</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>43935</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>43944</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>43945</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>43964</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>43964</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>43966</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>43966</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>43977</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>43983</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>43983</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>43986</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>43986</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44000</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>44000</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44007</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44007</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44022</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44032</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44036</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44039</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44060</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44064</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44064</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44069</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44071</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44075</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>44078</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44088</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44092</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44092</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44092</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>44092</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44092</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>44097</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>44105</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>44105</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44109</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44118</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>44129</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>44144</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44151</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44153</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44154</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44155</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44161</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44162</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44162</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>44165</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44169</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44172</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>44186</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>44186</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44193</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44195</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44208</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44211</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>44211</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44211</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>44216</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44216</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44235</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44235</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44235</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44235</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44235</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44235</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44235</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44237</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>44243</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>44246</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>44253</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>44253</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>44266</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44307</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44307</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44307</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44307</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44307</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44316</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44316</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44328</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44330</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44341</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44341</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44350</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44356</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44357</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44361</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44361</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44361</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44361</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44370</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44371</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44371</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44371</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44371</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44377</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44378</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>44382</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44386</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44389</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44389</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>44389</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44389</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44397</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44406</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44412</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44420</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>44420</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>44420</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44420</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>44420</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>44420</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44420</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>44419</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>44426</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>44433</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>44434</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44442</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44442</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44443</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44442</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>44452</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44452</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44452</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44452</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44452</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>44453</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44461</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44461</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>44462</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44469</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44470</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44473</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>44476</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>44476</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>44481</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>44482</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>44482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>44482</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44484</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44485</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44488</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44488</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44489</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44491</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44496</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44498</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44500</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>44502</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44503</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>44505</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>44511</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44515</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44515</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44515</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44522</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44522</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>44525</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44529</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>44531</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>44531</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44532</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44532</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44532</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44532</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>44533</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>44537</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44540</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44543</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44545</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44545</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44545</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44545</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>44545</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>44545</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44564</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>44567</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>44568</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>44578</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>44578</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>44594</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>44604</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>44609</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>44609</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>44615</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44615</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44617</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44617</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>44617</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>44617</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44617</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>44619</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44619</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44619</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44619</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44621</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44621</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44622</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44623</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44625</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44627</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44627</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44628</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44628</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44628</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44628</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44637</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44640</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         <v>44642</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>44657</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>44657</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>44658</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>44679</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44679</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44686</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44686</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44690</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44690</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>44692</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44693</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44693</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44698</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>44698</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>44700</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>44701</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>44708</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>44708</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44708</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44712</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>44713</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>44719</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>44726</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44725</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>44733</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38738,7 +38738,7 @@
         <v>44735</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>44735</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>44735</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44735</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>44741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44743</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44743</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>44743</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>44743</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44743</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>44743</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44743</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44743</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44743</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>44743</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44744</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>44744</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>44744</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44744</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>44744</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>44744</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44747</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>44747</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44748</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>44748</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>44754</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>44755</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>44756</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>44756</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>44757</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>44757</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>44757</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>44757</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>44773</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>44784</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>44784</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>44788</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44788</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>44788</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>44789</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44790</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>44797</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>44797</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41369,7 +41369,7 @@
         <v>44799</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>44798</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44799</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44799</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>44799</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44803</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>44802</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44802</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>44803</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44806</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>44805</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>44805</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44806</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>44810</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>44810</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>44813</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>44812</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44813</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44813</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44817</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44824</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>44824</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>44826</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>44827</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>44827</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>44826</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>44832</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>44831</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43204,7 +43204,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44834</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>44837</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>44837</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>44844</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>44847</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>44847</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>44847</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>44847</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>44847</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>44852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>44853</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>44852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>44853</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>44853</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>44852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>44853</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>44853</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>44855</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>44857</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>44859</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>44859</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>44858</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>44859</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44859</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>44858</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44859</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>44859</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>44859</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>44859</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>44862</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>44867</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44867</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45324,7 +45324,7 @@
         <v>44872</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>44874</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>44874</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>44875</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44879</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44879</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44881</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44881</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44888</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>44889</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>44889</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>44889</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44889</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44890</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44890</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>44890</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>44893</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>44896</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>44896</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>44901</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>44903</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>44903</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>44909</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>44909</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>44911</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>44911</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>44914</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>44917</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>44917</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>44917</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>44917</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>44920</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>44923</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44923</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>44923</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>44928</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>44930</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>44935</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>44936</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>44938</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>44938</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>44939</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>44939</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44939</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>44939</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>44939</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>44939</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>44939</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>44939</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44939</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>44939</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>44939</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>44939</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49127,7 +49127,7 @@
         <v>44942</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44943</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44944</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44944</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>44944</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>44945</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>44954</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>44955</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49878,7 +49878,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>44957</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>44960</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>44960</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>44960</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>44960</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>44960</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>44960</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>44963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>44971</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>44972</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>44972</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44972</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>44972</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>44972</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50959,7 +50959,7 @@
         <v>44972</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>44972</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>44972</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>44972</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>44972</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>44972</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>44972</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>44973</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>44978</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>44977</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>44977</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>44977</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>44978</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51755,7 +51755,7 @@
         <v>44981</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>44984</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>44985</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>44985</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>44985</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>44985</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>44985</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>44985</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>44987</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>44993</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>44993</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>44993</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>44994</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>44994</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>44995</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>45000</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52697,7 +52697,7 @@
         <v>45000</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>45000</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>45021</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52873,7 +52873,7 @@
         <v>45043</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45042</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>45043</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45048</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45048</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>45048</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53225,7 +53225,7 @@
         <v>45051</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45054</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>45056</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         <v>45056</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53463,7 +53463,7 @@
         <v>45057</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53525,7 +53525,7 @@
         <v>45062</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45076</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45084</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45084</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45084</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>45087</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53887,7 +53887,7 @@
         <v>45089</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>45089</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54001,7 +54001,7 @@
         <v>45089</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45090</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54120,7 +54120,7 @@
         <v>45090</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>45092</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>45093</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45092</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54363,7 +54363,7 @@
         <v>45092</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54420,7 +54420,7 @@
         <v>45093</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>45093</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
         <v>45096</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>45096</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45098</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>45098</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54777,7 +54777,7 @@
         <v>45099</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>45103</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54901,7 +54901,7 @@
         <v>45104</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54963,7 +54963,7 @@
         <v>45104</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>45104</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         <v>45104</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55149,7 +55149,7 @@
         <v>45105</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45106</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>45107</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45112</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45112</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45113</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45113</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45113</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45115</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45115</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45117</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>45117</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45119</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>45119</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45119</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>45125</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56126,7 +56126,7 @@
         <v>45125</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45140</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56411,7 +56411,7 @@
         <v>45143</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45142</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45148</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45148</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56721,7 +56721,7 @@
         <v>45147</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>45147</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>45148</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>45147</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45148</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57031,7 +57031,7 @@
         <v>45148</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>45149</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57150,7 +57150,7 @@
         <v>45149</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>45149</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57336,7 +57336,7 @@
         <v>45150</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57398,7 +57398,7 @@
         <v>45150</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57460,7 +57460,7 @@
         <v>45150</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45150</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45150</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45150</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>45152</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57765,7 +57765,7 @@
         <v>45152</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57822,7 +57822,7 @@
         <v>45155</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>45154</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>45155</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58003,7 +58003,7 @@
         <v>45154</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58065,7 +58065,7 @@
         <v>45155</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>45155</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58179,7 +58179,7 @@
         <v>45156</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58236,7 +58236,7 @@
         <v>45158</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58293,7 +58293,7 @@
         <v>45159</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58350,7 +58350,7 @@
         <v>45161</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>45161</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45162</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58536,7 +58536,7 @@
         <v>45161</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -58593,7 +58593,7 @@
         <v>45163</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45166</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45170</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58774,7 +58774,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>45170</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>45171</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58955,7 +58955,7 @@
         <v>45171</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59017,7 +59017,7 @@
         <v>45171</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59079,7 +59079,7 @@
         <v>45171</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45171</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45171</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59265,7 +59265,7 @@
         <v>45170</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45173</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45177</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59446,7 +59446,7 @@
         <v>45177</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>45177</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>45186</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>45187</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>45187</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59741,7 +59741,7 @@
         <v>45188</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59803,7 +59803,7 @@
         <v>45187</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59865,7 +59865,7 @@
         <v>45188</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59922,7 +59922,7 @@
         <v>45189</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59984,7 +59984,7 @@
         <v>45189</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60046,7 +60046,7 @@
         <v>45190</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45190</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45190</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45194</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60398,7 +60398,7 @@
         <v>45194</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         <v>45195</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60517,7 +60517,7 @@
         <v>45195</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45196</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>45196</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60698,7 +60698,7 @@
         <v>45196</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60817,7 +60817,7 @@
         <v>45195</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45198</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60941,7 +60941,7 @@
         <v>45199</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>45199</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>45203</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45203</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61189,7 +61189,7 @@
         <v>45203</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61313,7 +61313,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>45205</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45205</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>45205</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45205</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61685,7 +61685,7 @@
         <v>45205</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>45207</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61809,7 +61809,7 @@
         <v>45207</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61871,7 +61871,7 @@
         <v>45207</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>45207</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61995,7 +61995,7 @@
         <v>45208</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>45209</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62114,7 +62114,7 @@
         <v>45210</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62171,7 +62171,7 @@
         <v>45212</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62233,7 +62233,7 @@
         <v>45212</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>45212</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         <v>45217</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>45217</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62481,7 +62481,7 @@
         <v>45217</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45217</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45217</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>45217</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45217</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45216</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62848,7 +62848,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62910,7 +62910,7 @@
         <v>45217</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45217</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>45218</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63096,7 +63096,7 @@
         <v>45222</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63158,7 +63158,7 @@
         <v>45223</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63220,7 +63220,7 @@
         <v>45224</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63282,7 +63282,7 @@
         <v>45225</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>45226</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63406,7 +63406,7 @@
         <v>45225</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63468,7 +63468,7 @@
         <v>45226</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63530,7 +63530,7 @@
         <v>45226</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>45226</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63654,7 +63654,7 @@
         <v>45226</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>45227</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45229</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45229</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63892,7 +63892,7 @@
         <v>45230</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -64006,7 +64006,7 @@
         <v>45232</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64063,7 +64063,7 @@
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64120,7 +64120,7 @@
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64234,7 +64234,7 @@
         <v>45232</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>45233</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64415,7 +64415,7 @@
         <v>45237</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64539,7 +64539,7 @@
         <v>45237</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64601,7 +64601,7 @@
         <v>45236</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>45237</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64725,7 +64725,7 @@
         <v>45238</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64787,7 +64787,7 @@
         <v>45238</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64849,7 +64849,7 @@
         <v>45238</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64911,7 +64911,7 @@
         <v>45238</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64973,7 +64973,7 @@
         <v>45238</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -65035,7 +65035,7 @@
         <v>45238</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65097,7 +65097,7 @@
         <v>45238</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>45238</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65221,7 +65221,7 @@
         <v>45238</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65283,7 +65283,7 @@
         <v>45238</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65340,7 +65340,7 @@
         <v>45238</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65402,7 +65402,7 @@
         <v>45239</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65459,7 +65459,7 @@
         <v>45239</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65516,7 +65516,7 @@
         <v>45239</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65573,7 +65573,7 @@
         <v>45239</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>45239</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65680,14 +65680,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 56246-2023</t>
+          <t>A 56245-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65705,7 +65705,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -65742,14 +65742,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 56245-2023</t>
+          <t>A 56246-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65767,7 +65767,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -65804,14 +65804,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 56235-2023</t>
+          <t>A 56236-2023</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65824,7 +65824,7 @@
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>12.7</v>
+        <v>6.1</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -65861,14 +65861,14 @@
     <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 56236-2023</t>
+          <t>A 56235-2023</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65881,7 +65881,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>6.1</v>
+        <v>12.7</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -65918,14 +65918,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 57691-2023</t>
+          <t>A 56617-2023</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65938,7 +65938,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -65975,14 +65975,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 56617-2023</t>
+          <t>A 56622-2023</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -65995,7 +65995,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -66032,14 +66032,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 56622-2023</t>
+          <t>A 57691-2023</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66052,7 +66052,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -66089,14 +66089,14 @@
     <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>A 57058-2023</t>
+          <t>A 57057-2023</t>
         </is>
       </c>
       <c r="B1019" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66109,7 +66109,7 @@
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -66146,14 +66146,14 @@
     <row r="1020" ht="15" customHeight="1">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>A 57057-2023</t>
+          <t>A 57058-2023</t>
         </is>
       </c>
       <c r="B1020" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66166,7 +66166,7 @@
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="H1020" t="n">
         <v>0</v>
@@ -66210,7 +66210,7 @@
         <v>45245</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66267,7 +66267,7 @@
         <v>45247</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66329,7 +66329,7 @@
         <v>45248</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66386,7 +66386,7 @@
         <v>45251</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66441,14 +66441,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 58749-2023</t>
+          <t>A 58756-2023</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66461,7 +66461,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -66498,14 +66498,14 @@
     <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>A 58756-2023</t>
+          <t>A 59117-2023</t>
         </is>
       </c>
       <c r="B1026" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66518,7 +66518,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -66555,14 +66555,14 @@
     <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 59117-2023</t>
+          <t>A 59110-2023</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66575,7 +66575,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>1</v>
+        <v>10.1</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -66612,14 +66612,14 @@
     <row r="1028" ht="15" customHeight="1">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>A 59110-2023</t>
+          <t>A 58749-2023</t>
         </is>
       </c>
       <c r="B1028" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -66632,7 +66632,7 @@
         </is>
       </c>
       <c r="G1028" t="n">
-        <v>10.1</v>
+        <v>2.8</v>
       </c>
       <c r="H1028" t="n">
         <v>0</v>
@@ -66676,7 +66676,7 @@
         <v>45252</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66726,14 +66726,14 @@
     <row r="1030" ht="15" customHeight="1">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>A 60035-2023</t>
+          <t>A 59664-2023</t>
         </is>
       </c>
       <c r="B1030" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66745,8 +66745,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1030" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="H1030" t="n">
         <v>0</v>
@@ -66790,7 +66795,7 @@
         <v>45254</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66852,7 +66857,7 @@
         <v>45255</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66907,14 +66912,14 @@
     <row r="1033" ht="15" customHeight="1">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>A 59664-2023</t>
+          <t>A 60035-2023</t>
         </is>
       </c>
       <c r="B1033" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66926,13 +66931,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1033" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1033" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="H1033" t="n">
         <v>0</v>
@@ -66976,7 +66976,7 @@
         <v>45259</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67026,14 +67026,14 @@
     <row r="1035" ht="15" customHeight="1">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>A 60841-2023</t>
+          <t>A 60842-2023</t>
         </is>
       </c>
       <c r="B1035" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -67046,7 +67046,7 @@
         </is>
       </c>
       <c r="G1035" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="H1035" t="n">
         <v>0</v>
@@ -67083,14 +67083,14 @@
     <row r="1036" ht="15" customHeight="1">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>A 60842-2023</t>
+          <t>A 60841-2023</t>
         </is>
       </c>
       <c r="B1036" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -67103,7 +67103,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -67140,14 +67140,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 61779-2023</t>
+          <t>A 61778-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -67165,7 +67165,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -67202,14 +67202,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 62021-2023</t>
+          <t>A 61777-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -67221,8 +67221,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1038" t="n">
-        <v>2.4</v>
+        <v>20.6</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -67259,14 +67264,14 @@
     <row r="1039" ht="15" customHeight="1">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>A 61777-2023</t>
+          <t>A 61973-2023</t>
         </is>
       </c>
       <c r="B1039" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -67278,13 +67283,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1039" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1039" t="n">
-        <v>20.6</v>
+        <v>24.9</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -67321,14 +67321,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 61778-2023</t>
+          <t>A 61779-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -67346,7 +67346,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -67383,14 +67383,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 61973-2023</t>
+          <t>A 62021-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -67403,7 +67403,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>24.9</v>
+        <v>2.4</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -67440,14 +67440,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 62015-2023</t>
+          <t>A 61780-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -67459,8 +67459,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1042" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -67497,14 +67502,14 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 61780-2023</t>
+          <t>A 62015-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -67516,13 +67521,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1043" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1043" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -564,7 +564,7 @@
         <v>44350</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>44972</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44753</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44118</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44494</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>44412</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>44644</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>44838</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>44074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44350</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45125</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>44494</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>43741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45154</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44266</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>44645</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45119</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>43731</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>44263</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>44412</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45050</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>44964</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45181</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45201</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45030</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45030</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>44522</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>44972</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45205</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44838</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>45054</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45201</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>43805</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44095</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44474</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44838</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>44945</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45156</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45201</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44838</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>43336</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44095</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44266</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44838</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45119</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45201</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45201</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>43781</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44361</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45119</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45201</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45205</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>43731</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44678</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45201</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45205</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>43336</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43983</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44211</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45149</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>43381</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>43677</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44000</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44664</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45125</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>45132</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>44199</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>45205</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45208</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43608</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43726</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44609</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45050</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44000</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44206</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>43432</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>43987</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44039</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44382</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44420</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44732</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44972</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45113</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43523</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43658</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>43731</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>43923</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43924</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44235</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>44309</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>44401</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44518</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>44648</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44781</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45098</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>45112</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45125</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45233</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>43741</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>43775</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>43833</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>43837</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44141</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44195</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44476</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44494</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44531</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44532</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44560</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44638</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>44827</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>44852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44960</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44964</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44972</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44994</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45105</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>45166</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45240</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43332</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43332</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>43335</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>43340</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>43340</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>43347</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43350</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43360</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43370</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43370</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43370</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43375</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43375</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43377</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43377</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43377</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43377</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>43377</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43377</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43384</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43384</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43389</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>43389</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>43389</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>43395</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>43402</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>43409</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>43412</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>43412</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>43418</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43432</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>43432</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>43432</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>43432</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43440</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43444</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43448</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43451</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43467</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43472</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43472</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43475</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43476</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43476</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43479</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43480</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>43480</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>43480</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>43487</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>43496</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>43497</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>43500</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>43501</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>43503</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>43507</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>43509</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43509</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43509</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43509</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43523</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43523</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43523</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>43523</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>43542</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>43542</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>43542</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>43545</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>43545</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>43545</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>43558</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>43559</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>43559</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>43564</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>43592</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>43592</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>43594</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>43594</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>43608</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>43608</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>43612</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>43613</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>43614</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>43614</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>43640</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>43640</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>43640</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>43640</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>43640</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>43641</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>43648</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>43648</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>43656</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>43661</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43661</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>43664</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43664</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43664</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43665</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43682</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43690</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43699</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43700</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>43703</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>43705</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43712</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43714</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>43721</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>43726</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>43728</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>43731</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>43733</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>43733</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>43733</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>43739</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>43741</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>43746</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>43749</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>43749</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>43753</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>43755</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>43762</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>43762</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>43765</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>43774</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>43775</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>43791</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>43803</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>43805</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>43808</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>43810</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>43815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>43833</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>43833</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>43833</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>43837</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>43837</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>43838</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>43838</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>43854</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>43858</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>43858</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>43896</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>43896</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>43896</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>43896</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>43909</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>43910</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>43913</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>43913</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>43913</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>43913</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>43913</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>43913</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>43913</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>43913</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>43914</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>43915</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>43915</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>43915</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>43915</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>43923</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>43923</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>43923</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>43927</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>43935</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>43944</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>43945</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>43964</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>43964</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>43966</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>43966</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>43977</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>43983</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>43983</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>43986</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>43986</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44000</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>44000</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44007</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44007</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44022</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44032</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44036</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44039</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44060</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44064</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44064</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44069</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44071</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44075</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>44078</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44088</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44092</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44092</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44092</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>44092</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44092</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>44097</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>44105</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>44105</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44109</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44118</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>44129</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>44144</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44151</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44153</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44154</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44155</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44161</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44162</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44162</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>44165</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44169</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44172</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>44186</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>44186</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44193</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44195</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44208</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44211</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>44211</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44211</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>44216</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44216</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44235</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44235</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44235</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44235</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44235</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44235</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44235</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44237</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>44243</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>44246</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>44253</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>44253</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>44266</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44307</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44307</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44307</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44307</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44307</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44316</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44316</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44328</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44330</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44341</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44341</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44350</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44356</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44357</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44361</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44361</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44361</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44361</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44370</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44371</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44371</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44371</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44371</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44377</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44378</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>44382</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44386</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44389</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44389</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>44389</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44389</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44397</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44406</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44412</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44420</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>44420</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>44420</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44420</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>44420</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>44420</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44420</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>44419</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>44426</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>44433</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>44434</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44442</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44442</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44443</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44442</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>44452</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44452</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44452</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44452</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44452</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>44453</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44461</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44461</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>44462</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44469</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44470</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44473</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>44476</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>44476</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>44481</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>44482</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>44482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>44482</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44484</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44485</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44488</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44488</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44489</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44491</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44496</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44498</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44500</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>44502</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44503</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>44505</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>44511</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44515</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44515</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44515</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44522</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44522</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>44525</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44529</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>44531</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>44531</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44532</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44532</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44532</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44532</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>44533</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>44537</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44540</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44543</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44545</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44545</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44545</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44545</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>44545</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>44545</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44564</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>44567</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>44568</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>44578</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>44578</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>44594</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>44604</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>44609</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>44609</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>44615</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44615</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44617</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44617</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>44617</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>44617</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44617</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>44619</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44619</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44619</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44619</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44621</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44621</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44622</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44623</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44625</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44627</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44627</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44628</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44628</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44628</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44628</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44637</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44640</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         <v>44642</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>44657</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>44657</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>44658</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>44679</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44679</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44686</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44686</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44690</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44690</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>44692</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44693</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44693</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44698</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>44698</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>44700</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>44701</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>44708</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>44708</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44708</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44712</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>44713</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>44719</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>44726</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44725</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>44733</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38738,7 +38738,7 @@
         <v>44735</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>44735</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>44735</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44735</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>44741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44743</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44743</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>44743</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>44743</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44743</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>44743</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44743</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44743</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44743</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>44743</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44744</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>44744</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>44744</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44744</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>44744</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>44744</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44747</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>44747</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44748</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>44748</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>44754</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>44755</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>44756</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>44756</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>44757</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>44757</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>44757</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>44757</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>44773</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>44784</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>44784</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>44788</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44788</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>44788</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>44789</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44790</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>44797</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>44797</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41369,7 +41369,7 @@
         <v>44799</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>44798</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44799</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44799</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>44799</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44803</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>44802</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44802</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>44803</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44806</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>44805</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>44805</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44806</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>44810</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>44810</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>44813</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>44812</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44813</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44813</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44817</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44824</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>44824</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>44826</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>44827</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>44827</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>44826</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>44832</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>44831</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43204,7 +43204,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44834</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>44837</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>44837</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>44844</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>44847</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>44847</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>44847</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>44847</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>44847</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>44852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>44853</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>44852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>44853</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>44853</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>44852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>44853</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>44853</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>44855</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>44857</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>44859</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>44859</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>44858</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>44859</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44859</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>44858</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44859</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>44859</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>44859</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>44859</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>44862</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>44867</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44867</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45324,7 +45324,7 @@
         <v>44872</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>44874</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>44874</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>44875</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44879</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44879</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44881</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44881</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44888</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>44889</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>44889</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>44889</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44889</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44890</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44890</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>44890</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>44893</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>44896</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>44896</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>44901</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>44903</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>44903</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>44909</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>44909</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>44911</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>44911</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>44914</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>44917</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>44917</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>44917</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>44917</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>44920</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>44923</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44923</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>44923</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>44928</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>44930</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>44935</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>44936</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>44938</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>44938</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>44939</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>44939</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44939</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>44939</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>44939</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>44939</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>44939</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>44939</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44939</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>44939</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>44939</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>44939</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49127,7 +49127,7 @@
         <v>44942</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44943</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44944</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44944</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>44944</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>44945</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>44954</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>44955</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49878,7 +49878,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>44957</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>44960</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>44960</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>44960</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>44960</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>44960</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>44960</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>44963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>44971</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>44972</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>44972</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44972</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>44972</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>44972</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50959,7 +50959,7 @@
         <v>44972</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>44972</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>44972</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>44972</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>44972</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>44972</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>44972</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>44973</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>44978</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>44977</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>44977</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>44977</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>44978</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51755,7 +51755,7 @@
         <v>44981</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>44984</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>44985</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>44985</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>44985</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>44985</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>44985</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>44985</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>44987</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>44993</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>44993</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>44993</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>44994</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>44994</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>44995</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>45000</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52697,7 +52697,7 @@
         <v>45000</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>45000</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>45021</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52873,7 +52873,7 @@
         <v>45043</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45042</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>45043</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45048</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45048</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>45048</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53225,7 +53225,7 @@
         <v>45051</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45054</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>45056</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         <v>45056</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53463,7 +53463,7 @@
         <v>45057</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53525,7 +53525,7 @@
         <v>45062</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45076</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45084</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45084</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45084</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>45087</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53887,7 +53887,7 @@
         <v>45089</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>45089</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54001,7 +54001,7 @@
         <v>45089</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45090</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54120,7 +54120,7 @@
         <v>45090</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>45092</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>45093</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45092</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54363,7 +54363,7 @@
         <v>45092</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54420,7 +54420,7 @@
         <v>45093</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>45093</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
         <v>45096</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>45096</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45098</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>45098</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54777,7 +54777,7 @@
         <v>45099</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>45103</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54901,7 +54901,7 @@
         <v>45104</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54963,7 +54963,7 @@
         <v>45104</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>45104</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         <v>45104</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55149,7 +55149,7 @@
         <v>45105</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45106</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>45107</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45112</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45112</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45113</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45113</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45113</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45115</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45115</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45117</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>45117</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45119</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>45119</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45119</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>45125</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56126,7 +56126,7 @@
         <v>45125</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45140</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56411,7 +56411,7 @@
         <v>45143</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45142</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45148</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45148</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56721,7 +56721,7 @@
         <v>45147</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>45147</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>45148</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>45147</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45148</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57031,7 +57031,7 @@
         <v>45148</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>45149</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57150,7 +57150,7 @@
         <v>45149</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>45149</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57336,7 +57336,7 @@
         <v>45150</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57398,7 +57398,7 @@
         <v>45150</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57460,7 +57460,7 @@
         <v>45150</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45150</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45150</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45150</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>45152</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57765,7 +57765,7 @@
         <v>45152</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57822,7 +57822,7 @@
         <v>45155</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>45154</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>45155</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58003,7 +58003,7 @@
         <v>45154</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58065,7 +58065,7 @@
         <v>45155</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>45155</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58179,7 +58179,7 @@
         <v>45156</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58236,7 +58236,7 @@
         <v>45158</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58293,7 +58293,7 @@
         <v>45159</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58350,7 +58350,7 @@
         <v>45161</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>45161</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45162</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58536,7 +58536,7 @@
         <v>45161</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -58593,7 +58593,7 @@
         <v>45163</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45166</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45170</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58774,7 +58774,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>45170</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>45171</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58955,7 +58955,7 @@
         <v>45171</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59017,7 +59017,7 @@
         <v>45171</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59079,7 +59079,7 @@
         <v>45171</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45171</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45171</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59265,7 +59265,7 @@
         <v>45170</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45173</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45177</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59446,7 +59446,7 @@
         <v>45177</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>45177</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>45186</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>45187</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>45187</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59741,7 +59741,7 @@
         <v>45188</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59803,7 +59803,7 @@
         <v>45187</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59865,7 +59865,7 @@
         <v>45188</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59922,7 +59922,7 @@
         <v>45189</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59984,7 +59984,7 @@
         <v>45189</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60046,7 +60046,7 @@
         <v>45190</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45190</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45190</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45194</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60398,7 +60398,7 @@
         <v>45194</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         <v>45195</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60517,7 +60517,7 @@
         <v>45195</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45196</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>45196</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60698,7 +60698,7 @@
         <v>45196</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60817,7 +60817,7 @@
         <v>45195</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45198</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60941,7 +60941,7 @@
         <v>45199</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>45199</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>45203</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45203</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61189,7 +61189,7 @@
         <v>45203</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61313,7 +61313,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>45205</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45205</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>45205</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45205</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61685,7 +61685,7 @@
         <v>45205</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>45207</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61809,7 +61809,7 @@
         <v>45207</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61871,7 +61871,7 @@
         <v>45207</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>45207</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61995,7 +61995,7 @@
         <v>45208</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>45209</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62114,7 +62114,7 @@
         <v>45210</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62171,7 +62171,7 @@
         <v>45212</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62233,7 +62233,7 @@
         <v>45212</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>45212</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         <v>45217</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>45217</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62481,7 +62481,7 @@
         <v>45217</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45217</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45217</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>45217</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45217</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45216</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62848,7 +62848,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62910,7 +62910,7 @@
         <v>45217</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45217</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>45218</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63096,7 +63096,7 @@
         <v>45222</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63158,7 +63158,7 @@
         <v>45223</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63220,7 +63220,7 @@
         <v>45224</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63282,7 +63282,7 @@
         <v>45225</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>45226</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63406,7 +63406,7 @@
         <v>45225</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63468,7 +63468,7 @@
         <v>45226</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63530,7 +63530,7 @@
         <v>45226</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>45226</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63654,7 +63654,7 @@
         <v>45226</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>45227</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45229</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45229</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63892,7 +63892,7 @@
         <v>45230</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -64006,7 +64006,7 @@
         <v>45232</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64063,7 +64063,7 @@
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64120,7 +64120,7 @@
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64234,7 +64234,7 @@
         <v>45232</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>45233</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64415,7 +64415,7 @@
         <v>45237</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64539,7 +64539,7 @@
         <v>45237</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64601,7 +64601,7 @@
         <v>45236</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>45237</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64725,7 +64725,7 @@
         <v>45238</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64787,7 +64787,7 @@
         <v>45238</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64849,7 +64849,7 @@
         <v>45238</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64911,7 +64911,7 @@
         <v>45238</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64973,7 +64973,7 @@
         <v>45238</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -65035,7 +65035,7 @@
         <v>45238</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65097,7 +65097,7 @@
         <v>45238</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>45238</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65221,7 +65221,7 @@
         <v>45238</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65283,7 +65283,7 @@
         <v>45238</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65340,7 +65340,7 @@
         <v>45238</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65402,7 +65402,7 @@
         <v>45239</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65459,7 +65459,7 @@
         <v>45239</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65516,7 +65516,7 @@
         <v>45239</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65573,7 +65573,7 @@
         <v>45239</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>45239</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65687,7 +65687,7 @@
         <v>45240</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65749,7 +65749,7 @@
         <v>45240</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65811,7 +65811,7 @@
         <v>45240</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65868,7 +65868,7 @@
         <v>45240</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65918,14 +65918,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 56617-2023</t>
+          <t>A 56622-2023</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65938,7 +65938,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -65975,14 +65975,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 56622-2023</t>
+          <t>A 56617-2023</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -65995,7 +65995,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -66039,7 +66039,7 @@
         <v>45243</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66096,7 +66096,7 @@
         <v>45244</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66153,7 +66153,7 @@
         <v>45244</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66210,7 +66210,7 @@
         <v>45245</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66267,7 +66267,7 @@
         <v>45247</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66329,7 +66329,7 @@
         <v>45248</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66386,7 +66386,7 @@
         <v>45251</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66441,14 +66441,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 58756-2023</t>
+          <t>A 58749-2023</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66461,7 +66461,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -66498,14 +66498,14 @@
     <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>A 59117-2023</t>
+          <t>A 58756-2023</t>
         </is>
       </c>
       <c r="B1026" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66518,7 +66518,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -66562,7 +66562,7 @@
         <v>45251</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66612,14 +66612,14 @@
     <row r="1028" ht="15" customHeight="1">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>A 58749-2023</t>
+          <t>A 59117-2023</t>
         </is>
       </c>
       <c r="B1028" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -66632,7 +66632,7 @@
         </is>
       </c>
       <c r="G1028" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="H1028" t="n">
         <v>0</v>
@@ -66676,7 +66676,7 @@
         <v>45252</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66733,7 +66733,7 @@
         <v>45254</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66795,7 +66795,7 @@
         <v>45254</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66857,7 +66857,7 @@
         <v>45255</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>45254</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66976,7 +66976,7 @@
         <v>45259</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67033,7 +67033,7 @@
         <v>45260</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -67090,7 +67090,7 @@
         <v>45260</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -67147,7 +67147,7 @@
         <v>45265</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -67202,14 +67202,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 61777-2023</t>
+          <t>A 61779-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -67227,7 +67227,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>20.6</v>
+        <v>2</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -67264,14 +67264,14 @@
     <row r="1039" ht="15" customHeight="1">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>A 61973-2023</t>
+          <t>A 61777-2023</t>
         </is>
       </c>
       <c r="B1039" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -67283,8 +67283,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1039" t="n">
-        <v>24.9</v>
+        <v>20.6</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -67321,14 +67326,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 61779-2023</t>
+          <t>A 61973-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -67340,13 +67345,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1040" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1040" t="n">
-        <v>2</v>
+        <v>24.9</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -67383,14 +67383,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 62021-2023</t>
+          <t>A 61780-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -67402,8 +67402,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1041" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -67440,14 +67445,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 61780-2023</t>
+          <t>A 62015-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -67459,13 +67464,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1042" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1042" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -67502,14 +67502,14 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 62015-2023</t>
+          <t>A 62021-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -67522,7 +67522,7 @@
         </is>
       </c>
       <c r="G1043" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -564,7 +564,7 @@
         <v>44350</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>44972</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44753</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44118</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44494</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>44412</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>44644</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>44838</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>44074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44350</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45125</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>44494</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>43741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45154</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44266</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>44645</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45119</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>43731</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>44263</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>44412</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45050</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>44964</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45181</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45201</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45030</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45030</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>44522</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>44972</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45205</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44838</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>45054</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45201</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>43805</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44095</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44474</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44838</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>44945</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45156</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45201</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44838</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>43336</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44095</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44266</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44838</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45119</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45201</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45201</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>43781</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44361</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45119</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45201</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45205</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>43731</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44678</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45201</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45205</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>43336</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43983</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44211</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45149</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>43381</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>43677</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44000</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44664</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45125</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>45132</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>44199</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>45205</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45208</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43608</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43726</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44609</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45050</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44000</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44206</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>43432</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>43987</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44039</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44382</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44420</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44732</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44972</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45113</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43523</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43658</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>43731</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>43923</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43924</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44235</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>44309</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>44401</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44518</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>44648</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44781</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45098</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>45112</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45125</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45233</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>43741</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>43775</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>43833</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>43837</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44141</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44195</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44476</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44494</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44531</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44532</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44560</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44638</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>44827</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>44852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44960</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44964</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44972</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44994</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45105</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>45166</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45240</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43332</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43332</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>43335</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>43340</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>43340</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>43347</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43350</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43360</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43370</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43370</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43370</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43375</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43375</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43377</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43377</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43377</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43377</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>43377</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43377</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43384</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43384</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43389</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>43389</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>43389</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>43395</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>43402</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>43409</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>43412</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>43412</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>43418</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43432</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>43432</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>43432</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>43432</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43440</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43444</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43448</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43451</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43467</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43472</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43472</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43475</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43476</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43476</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43479</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43480</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>43480</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>43480</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>43487</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>43496</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>43497</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>43500</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>43501</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>43503</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>43507</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>43509</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43509</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43509</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43509</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43523</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43523</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43523</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>43523</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>43542</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>43542</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>43542</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>43545</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>43545</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>43545</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>43558</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>43559</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>43559</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>43564</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>43592</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>43592</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>43594</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>43594</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>43608</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>43608</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>43612</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>43613</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>43614</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>43614</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>43640</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>43640</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>43640</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>43640</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>43640</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>43641</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>43648</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>43648</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>43656</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>43661</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43661</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>43664</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43664</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43664</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43665</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43682</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43690</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43699</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43700</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>43703</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>43705</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43712</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43714</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>43721</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>43726</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>43728</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>43731</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>43733</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>43733</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>43733</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>43739</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>43741</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>43746</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>43749</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>43749</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>43753</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>43755</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>43762</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>43762</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>43765</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>43774</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>43775</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>43791</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>43803</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>43805</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>43808</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>43810</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>43815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>43833</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>43833</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>43833</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>43837</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>43837</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>43838</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>43838</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>43854</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>43858</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>43858</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>43896</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>43896</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>43896</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>43896</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>43909</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>43910</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>43913</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>43913</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>43913</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>43913</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>43913</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>43913</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>43913</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>43913</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>43914</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>43915</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>43915</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>43915</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>43915</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>43923</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>43923</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>43923</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>43927</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>43935</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>43944</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>43945</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>43964</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>43964</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>43966</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>43966</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>43977</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>43983</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>43983</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>43986</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>43986</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44000</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>44000</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44007</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44007</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44022</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44032</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44036</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44039</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44060</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44064</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44064</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44069</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44071</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44075</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>44078</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44088</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44092</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44092</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44092</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>44092</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44092</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>44097</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>44105</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>44105</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44109</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44118</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>44129</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>44144</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44151</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44153</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44154</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44155</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44161</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44162</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44162</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>44165</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44169</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44172</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>44186</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>44186</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44193</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44195</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44208</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44211</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>44211</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44211</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>44216</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44216</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44235</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44235</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44235</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44235</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44235</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44235</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44235</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44237</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>44243</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>44246</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>44253</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>44253</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>44266</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44307</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44307</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44307</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44307</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44307</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44316</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44316</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44328</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44330</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44341</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44341</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44350</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44356</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44357</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44361</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44361</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44361</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44361</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44370</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44371</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44371</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44371</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44371</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44377</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44378</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>44382</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44386</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44389</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44389</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>44389</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44389</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44397</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44406</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44412</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44420</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>44420</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>44420</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44420</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>44420</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>44420</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44420</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>44419</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>44426</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>44433</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>44434</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44442</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44442</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44443</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44442</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>44452</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44452</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44452</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44452</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44452</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>44453</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44461</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44461</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>44462</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44469</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44470</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44473</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>44476</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>44476</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>44481</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>44482</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>44482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>44482</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44484</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44485</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44488</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44488</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44489</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44491</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44496</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44498</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44500</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>44502</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44503</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>44505</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>44511</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44515</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44515</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44515</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44522</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44522</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>44525</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44529</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>44531</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>44531</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44532</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44532</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44532</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44532</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>44533</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>44537</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44540</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44543</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44545</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44545</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44545</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44545</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>44545</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>44545</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44564</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>44567</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>44568</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>44578</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>44578</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>44594</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>44604</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>44609</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>44609</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>44615</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44615</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44617</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44617</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>44617</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>44617</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44617</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>44619</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44619</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44619</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44619</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44621</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44621</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44622</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44623</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44625</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44627</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44627</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44628</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44628</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44628</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44628</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44637</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44640</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         <v>44642</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>44657</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>44657</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>44658</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>44679</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44679</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44686</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44686</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44690</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44690</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>44692</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44693</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44693</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44698</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>44698</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>44700</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>44701</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>44708</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>44708</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44708</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44712</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>44713</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>44719</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>44726</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44725</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>44733</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38738,7 +38738,7 @@
         <v>44735</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>44735</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>44735</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44735</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>44741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44743</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44743</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>44743</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>44743</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44743</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>44743</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44743</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44743</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44743</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>44743</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44744</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>44744</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>44744</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44744</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>44744</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>44744</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44747</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>44747</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44748</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>44748</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>44754</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>44755</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>44756</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>44756</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>44757</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>44757</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>44757</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>44757</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>44773</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>44784</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>44784</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>44788</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44788</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>44788</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>44789</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44790</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>44797</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>44797</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41369,7 +41369,7 @@
         <v>44799</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>44798</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44799</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44799</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>44799</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44803</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>44802</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44802</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>44803</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44806</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>44805</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>44805</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44806</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>44810</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>44810</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>44813</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>44812</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44813</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44813</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44817</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44824</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>44824</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>44826</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>44827</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>44827</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>44826</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>44832</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>44831</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43204,7 +43204,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44834</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>44837</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>44837</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>44844</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>44847</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>44847</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>44847</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>44847</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>44847</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>44852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>44853</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>44852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>44853</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>44853</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>44852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>44853</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>44853</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>44855</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>44857</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>44859</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>44859</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>44858</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>44859</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44859</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>44858</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44859</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>44859</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>44859</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>44859</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>44862</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>44867</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44867</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45324,7 +45324,7 @@
         <v>44872</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>44874</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>44874</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>44875</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44879</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44879</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44881</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44881</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44888</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>44889</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>44889</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>44889</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44889</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44890</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44890</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>44890</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>44893</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>44896</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>44896</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>44901</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>44903</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>44903</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>44909</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>44909</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>44911</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>44911</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>44914</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>44917</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>44917</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>44917</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>44917</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>44920</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>44923</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44923</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>44923</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>44928</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>44930</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>44935</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>44936</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>44938</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>44938</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>44939</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>44939</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44939</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>44939</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>44939</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>44939</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>44939</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>44939</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44939</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>44939</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>44939</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>44939</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49127,7 +49127,7 @@
         <v>44942</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44943</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44944</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44944</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>44944</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>44945</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>44954</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>44955</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49878,7 +49878,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>44957</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>44960</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>44960</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>44960</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>44960</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>44960</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>44960</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>44963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>44971</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>44972</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>44972</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44972</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>44972</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>44972</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50959,7 +50959,7 @@
         <v>44972</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>44972</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>44972</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>44972</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>44972</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>44972</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>44972</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>44973</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>44978</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>44977</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>44977</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>44977</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>44978</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51755,7 +51755,7 @@
         <v>44981</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>44984</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>44985</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>44985</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>44985</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>44985</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>44985</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>44985</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>44987</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>44993</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>44993</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>44993</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>44994</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>44994</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>44995</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>45000</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52697,7 +52697,7 @@
         <v>45000</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>45000</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>45021</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52873,7 +52873,7 @@
         <v>45043</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45042</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>45043</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45048</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45048</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>45048</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53225,7 +53225,7 @@
         <v>45051</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45054</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>45056</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         <v>45056</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53463,7 +53463,7 @@
         <v>45057</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53525,7 +53525,7 @@
         <v>45062</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45076</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45084</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45084</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45084</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>45087</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53887,7 +53887,7 @@
         <v>45089</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>45089</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54001,7 +54001,7 @@
         <v>45089</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45090</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54120,7 +54120,7 @@
         <v>45090</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>45092</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>45093</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45092</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54363,7 +54363,7 @@
         <v>45092</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54420,7 +54420,7 @@
         <v>45093</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>45093</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
         <v>45096</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>45096</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45098</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>45098</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54777,7 +54777,7 @@
         <v>45099</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>45103</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54901,7 +54901,7 @@
         <v>45104</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54963,7 +54963,7 @@
         <v>45104</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>45104</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         <v>45104</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55149,7 +55149,7 @@
         <v>45105</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45106</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>45107</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45112</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45112</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45113</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45113</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45113</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45115</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45115</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45117</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>45117</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45119</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>45119</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45119</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>45125</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56126,7 +56126,7 @@
         <v>45125</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45140</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56411,7 +56411,7 @@
         <v>45143</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45142</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45148</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45148</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56721,7 +56721,7 @@
         <v>45147</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>45147</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>45148</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>45147</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45148</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57031,7 +57031,7 @@
         <v>45148</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>45149</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57150,7 +57150,7 @@
         <v>45149</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>45149</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57336,7 +57336,7 @@
         <v>45150</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57398,7 +57398,7 @@
         <v>45150</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57460,7 +57460,7 @@
         <v>45150</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45150</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45150</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45150</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>45152</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57765,7 +57765,7 @@
         <v>45152</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57822,7 +57822,7 @@
         <v>45155</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>45154</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>45155</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58003,7 +58003,7 @@
         <v>45154</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58065,7 +58065,7 @@
         <v>45155</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>45155</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58179,7 +58179,7 @@
         <v>45156</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58236,7 +58236,7 @@
         <v>45158</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58293,7 +58293,7 @@
         <v>45159</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58350,7 +58350,7 @@
         <v>45161</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>45161</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45162</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58536,7 +58536,7 @@
         <v>45161</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -58593,7 +58593,7 @@
         <v>45163</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45166</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45170</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58774,7 +58774,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>45170</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>45171</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58955,7 +58955,7 @@
         <v>45171</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59017,7 +59017,7 @@
         <v>45171</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59079,7 +59079,7 @@
         <v>45171</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45171</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45171</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59265,7 +59265,7 @@
         <v>45170</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45173</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45177</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59446,7 +59446,7 @@
         <v>45177</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>45177</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>45186</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>45187</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>45187</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59741,7 +59741,7 @@
         <v>45188</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59803,7 +59803,7 @@
         <v>45187</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59865,7 +59865,7 @@
         <v>45188</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59922,7 +59922,7 @@
         <v>45189</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59984,7 +59984,7 @@
         <v>45189</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60046,7 +60046,7 @@
         <v>45190</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45190</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45190</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45194</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60398,7 +60398,7 @@
         <v>45194</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         <v>45195</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60517,7 +60517,7 @@
         <v>45195</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45196</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>45196</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60698,7 +60698,7 @@
         <v>45196</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60817,7 +60817,7 @@
         <v>45195</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45198</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60941,7 +60941,7 @@
         <v>45199</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>45199</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>45203</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45203</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61189,7 +61189,7 @@
         <v>45203</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61313,7 +61313,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>45205</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45205</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>45205</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45205</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61685,7 +61685,7 @@
         <v>45205</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>45207</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61809,7 +61809,7 @@
         <v>45207</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61871,7 +61871,7 @@
         <v>45207</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>45207</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61995,7 +61995,7 @@
         <v>45208</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>45209</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62114,7 +62114,7 @@
         <v>45210</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62171,7 +62171,7 @@
         <v>45212</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62233,7 +62233,7 @@
         <v>45212</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>45212</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         <v>45217</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>45217</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62481,7 +62481,7 @@
         <v>45217</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45217</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45217</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>45217</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45217</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45216</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62848,7 +62848,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62910,7 +62910,7 @@
         <v>45217</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45217</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>45218</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63096,7 +63096,7 @@
         <v>45222</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63158,7 +63158,7 @@
         <v>45223</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63220,7 +63220,7 @@
         <v>45224</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63282,7 +63282,7 @@
         <v>45225</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>45226</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63406,7 +63406,7 @@
         <v>45225</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63468,7 +63468,7 @@
         <v>45226</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63530,7 +63530,7 @@
         <v>45226</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>45226</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63654,7 +63654,7 @@
         <v>45226</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>45227</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45229</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45229</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63892,7 +63892,7 @@
         <v>45230</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -64006,7 +64006,7 @@
         <v>45232</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64063,7 +64063,7 @@
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64120,7 +64120,7 @@
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64234,7 +64234,7 @@
         <v>45232</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>45233</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64415,7 +64415,7 @@
         <v>45237</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64539,7 +64539,7 @@
         <v>45237</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64601,7 +64601,7 @@
         <v>45236</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>45237</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64725,7 +64725,7 @@
         <v>45238</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64787,7 +64787,7 @@
         <v>45238</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64849,7 +64849,7 @@
         <v>45238</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64911,7 +64911,7 @@
         <v>45238</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64973,7 +64973,7 @@
         <v>45238</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -65035,7 +65035,7 @@
         <v>45238</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65097,7 +65097,7 @@
         <v>45238</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>45238</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65221,7 +65221,7 @@
         <v>45238</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65283,7 +65283,7 @@
         <v>45238</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65340,7 +65340,7 @@
         <v>45238</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65402,7 +65402,7 @@
         <v>45239</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65459,7 +65459,7 @@
         <v>45239</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65516,7 +65516,7 @@
         <v>45239</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65573,7 +65573,7 @@
         <v>45239</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>45239</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65687,7 +65687,7 @@
         <v>45240</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65749,7 +65749,7 @@
         <v>45240</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65811,7 +65811,7 @@
         <v>45240</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65868,7 +65868,7 @@
         <v>45240</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65918,14 +65918,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 56622-2023</t>
+          <t>A 56617-2023</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65938,7 +65938,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -65975,14 +65975,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 56617-2023</t>
+          <t>A 56622-2023</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -65995,7 +65995,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -66039,7 +66039,7 @@
         <v>45243</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66096,7 +66096,7 @@
         <v>45244</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66153,7 +66153,7 @@
         <v>45244</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66210,7 +66210,7 @@
         <v>45245</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66267,7 +66267,7 @@
         <v>45247</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66329,7 +66329,7 @@
         <v>45248</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66386,7 +66386,7 @@
         <v>45251</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66441,14 +66441,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 58749-2023</t>
+          <t>A 58756-2023</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66461,7 +66461,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -66498,14 +66498,14 @@
     <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>A 58756-2023</t>
+          <t>A 59117-2023</t>
         </is>
       </c>
       <c r="B1026" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66518,7 +66518,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -66562,7 +66562,7 @@
         <v>45251</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66612,14 +66612,14 @@
     <row r="1028" ht="15" customHeight="1">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>A 59117-2023</t>
+          <t>A 58749-2023</t>
         </is>
       </c>
       <c r="B1028" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -66632,7 +66632,7 @@
         </is>
       </c>
       <c r="G1028" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="H1028" t="n">
         <v>0</v>
@@ -66676,7 +66676,7 @@
         <v>45252</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66733,7 +66733,7 @@
         <v>45254</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66795,7 +66795,7 @@
         <v>45254</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66857,7 +66857,7 @@
         <v>45255</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>45254</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66976,7 +66976,7 @@
         <v>45259</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67026,14 +67026,14 @@
     <row r="1035" ht="15" customHeight="1">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>A 60842-2023</t>
+          <t>A 60841-2023</t>
         </is>
       </c>
       <c r="B1035" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -67046,7 +67046,7 @@
         </is>
       </c>
       <c r="G1035" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="H1035" t="n">
         <v>0</v>
@@ -67083,14 +67083,14 @@
     <row r="1036" ht="15" customHeight="1">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>A 60841-2023</t>
+          <t>A 60842-2023</t>
         </is>
       </c>
       <c r="B1036" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -67103,7 +67103,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -67140,14 +67140,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 61778-2023</t>
+          <t>A 61780-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -67165,7 +67165,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -67202,14 +67202,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 61779-2023</t>
+          <t>A 61777-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -67227,7 +67227,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>2</v>
+        <v>20.6</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -67264,14 +67264,14 @@
     <row r="1039" ht="15" customHeight="1">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>A 61777-2023</t>
+          <t>A 61973-2023</t>
         </is>
       </c>
       <c r="B1039" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -67283,13 +67283,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1039" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1039" t="n">
-        <v>20.6</v>
+        <v>24.9</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -67326,14 +67321,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 61973-2023</t>
+          <t>A 61778-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -67345,8 +67340,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1040" t="n">
-        <v>24.9</v>
+        <v>3.9</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -67383,14 +67383,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 61780-2023</t>
+          <t>A 62015-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -67402,13 +67402,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1041" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1041" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -67445,14 +67440,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 62015-2023</t>
+          <t>A 61779-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -67464,8 +67459,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1042" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -67509,7 +67509,7 @@
         <v>45265</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1043"/>
+  <dimension ref="A1:Y1045"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44350</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>44972</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44753</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44118</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44494</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>44412</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>44644</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>44838</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>44074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44350</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45125</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>44494</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>43741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45154</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44266</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>44645</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45119</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>43731</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>44263</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>44412</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45050</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>44964</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45181</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45201</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45030</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45030</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>44522</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>44972</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45205</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44838</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>45054</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45201</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>43805</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44095</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44474</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44838</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>44945</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45156</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45201</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44838</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>43336</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44095</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44266</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44838</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45119</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45201</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45201</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>43781</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44361</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45119</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45201</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45205</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>43731</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44678</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45201</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45205</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>43336</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43983</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44211</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45149</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>43381</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>43677</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44000</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44664</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45125</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>45132</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>44199</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>45205</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45208</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43608</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43726</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44609</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45050</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44000</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44206</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>43432</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>43987</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44039</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44382</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44420</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44732</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44972</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45113</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43523</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43658</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>43731</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>43923</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43924</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44235</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>44309</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>44401</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44518</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>44648</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44781</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45098</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>45112</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45125</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45233</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>43741</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>43775</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>43833</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>43837</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44141</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44195</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44476</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44494</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44531</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44532</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44560</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44638</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>44827</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>44852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44960</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44964</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44972</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44994</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45105</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>45166</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45240</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43332</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43332</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>43335</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>43340</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>43340</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>43347</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43350</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43360</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43370</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43370</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43370</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43375</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43375</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43377</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43377</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43377</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43377</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>43377</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43377</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43384</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43384</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43389</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>43389</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>43389</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>43395</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>43402</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>43409</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>43412</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>43412</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>43418</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43432</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>43432</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>43432</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>43432</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43440</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43444</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43448</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43451</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43467</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43472</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43472</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43475</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43476</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43476</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43479</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43480</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>43480</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>43480</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>43487</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>43496</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>43497</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>43500</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>43501</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>43503</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>43507</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>43509</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43509</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43509</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43509</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43523</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43523</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43523</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>43523</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>43542</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>43542</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>43542</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>43545</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>43545</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>43545</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>43558</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>43559</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>43559</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>43564</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>43592</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>43592</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>43594</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>43594</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>43608</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>43608</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>43612</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>43613</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>43614</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>43614</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>43640</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>43640</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>43640</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>43640</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>43640</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>43641</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>43648</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>43648</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>43656</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>43661</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43661</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>43664</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43664</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43664</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43665</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43682</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43690</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43699</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43700</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>43703</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>43705</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43712</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43714</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>43721</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>43726</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>43728</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>43731</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>43733</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>43733</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>43733</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>43739</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>43741</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>43746</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>43749</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>43749</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>43753</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>43755</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>43762</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>43762</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>43765</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>43774</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>43775</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>43791</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>43803</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>43805</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>43808</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>43810</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>43815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>43833</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>43833</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>43833</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>43837</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>43837</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>43838</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>43838</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>43854</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>43858</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>43858</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>43896</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>43896</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>43896</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>43896</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>43909</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>43910</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>43913</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>43913</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>43913</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>43913</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>43913</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>43913</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>43913</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>43913</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>43914</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>43915</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>43915</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>43915</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>43915</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>43923</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>43923</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>43923</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>43927</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>43935</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>43944</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>43945</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>43964</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>43964</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>43966</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>43966</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>43977</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>43983</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>43983</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>43986</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>43986</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44000</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>44000</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44007</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44007</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44022</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44032</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44036</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44039</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44060</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44064</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44064</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44069</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44071</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44075</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>44078</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44088</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44092</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44092</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44092</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>44092</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44092</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>44097</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>44105</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>44105</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44109</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44118</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>44129</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>44144</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44151</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44153</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44154</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44155</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44161</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44162</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44162</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>44165</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44169</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44172</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>44186</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>44186</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44193</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44195</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44208</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44211</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>44211</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44211</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>44216</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44216</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44235</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44235</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44235</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44235</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44235</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44235</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44235</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44237</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>44243</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>44246</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>44253</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>44253</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>44266</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44307</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44307</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44307</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44307</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44307</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44316</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44316</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44328</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44330</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44341</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44341</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44350</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44356</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44357</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44361</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44361</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44361</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44361</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44370</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44371</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44371</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44371</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44371</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44377</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44378</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>44382</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44386</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44389</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44389</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>44389</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44389</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44397</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44406</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44412</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44420</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>44420</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>44420</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44420</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>44420</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>44420</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44420</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>44419</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>44426</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>44433</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>44434</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44442</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44442</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44443</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44442</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>44452</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44452</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44452</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44452</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44452</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>44453</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44461</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44461</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>44462</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44469</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44470</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44473</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>44476</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>44476</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>44481</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>44482</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>44482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>44482</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44484</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44485</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44488</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44488</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44489</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44491</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44496</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44498</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44500</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>44502</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44503</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>44505</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>44511</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44515</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44515</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44515</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44522</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44522</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>44525</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44529</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>44531</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>44531</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44532</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44532</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44532</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44532</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>44533</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>44537</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44540</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44543</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44545</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44545</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44545</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44545</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>44545</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>44545</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44564</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>44567</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>44568</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>44578</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>44578</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>44594</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>44604</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>44609</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>44609</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>44615</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44615</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44617</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44617</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>44617</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>44617</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44617</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>44619</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44619</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44619</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44619</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44621</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44621</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44622</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44623</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44625</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44627</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44627</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44628</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44628</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44628</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44628</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44637</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44640</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         <v>44642</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>44657</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>44657</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>44658</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>44679</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44679</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44686</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44686</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44690</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44690</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>44692</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44693</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44693</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44698</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>44698</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>44700</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>44701</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>44708</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>44708</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44708</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44712</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>44713</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>44719</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>44726</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44725</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>44733</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38738,7 +38738,7 @@
         <v>44735</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>44735</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>44735</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44735</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>44741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44743</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44743</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>44743</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>44743</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44743</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>44743</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44743</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44743</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44743</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>44743</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44744</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>44744</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>44744</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44744</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>44744</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>44744</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44747</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>44747</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44748</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>44748</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>44754</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>44755</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>44756</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>44756</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>44757</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>44757</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>44757</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>44757</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>44773</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>44784</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>44784</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>44788</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44788</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>44788</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>44789</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44790</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>44797</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>44797</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41369,7 +41369,7 @@
         <v>44799</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>44798</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44799</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44799</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>44799</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44803</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>44802</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44802</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>44803</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44806</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>44805</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>44805</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44806</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>44810</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>44810</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>44813</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>44812</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44813</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44813</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44817</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44824</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>44824</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>44826</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>44827</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>44827</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>44826</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>44832</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>44831</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43204,7 +43204,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44834</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>44837</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>44837</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>44844</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>44847</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>44847</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>44847</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>44847</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>44847</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>44852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>44853</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>44852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>44853</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>44853</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>44852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>44853</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>44853</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>44855</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>44857</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>44859</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>44859</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>44858</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>44859</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44859</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>44858</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44859</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>44859</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>44859</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>44859</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>44862</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>44867</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44867</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45324,7 +45324,7 @@
         <v>44872</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>44874</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>44874</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>44875</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44879</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44879</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44881</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44881</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44888</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>44889</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>44889</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>44889</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44889</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44890</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44890</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>44890</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>44893</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>44896</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>44896</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>44901</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>44903</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>44903</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>44909</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>44909</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>44911</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>44911</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>44914</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>44917</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>44917</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>44917</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>44917</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>44920</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>44923</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44923</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>44923</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>44928</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>44930</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>44935</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>44936</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>44938</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>44938</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>44939</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>44939</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44939</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>44939</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>44939</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>44939</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>44939</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>44939</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44939</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>44939</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>44939</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>44939</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49127,7 +49127,7 @@
         <v>44942</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44943</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44944</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44944</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>44944</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>44945</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>44954</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>44955</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49878,7 +49878,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>44957</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>44960</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>44960</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>44960</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>44960</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>44960</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>44960</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>44963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>44971</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>44972</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>44972</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44972</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>44972</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>44972</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50959,7 +50959,7 @@
         <v>44972</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>44972</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>44972</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>44972</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>44972</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>44972</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>44972</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>44973</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>44978</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>44977</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>44977</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>44977</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>44978</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51755,7 +51755,7 @@
         <v>44981</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>44984</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>44985</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>44985</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>44985</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>44985</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>44985</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>44985</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>44987</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>44993</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>44993</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>44993</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>44994</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>44994</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>44995</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>45000</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52697,7 +52697,7 @@
         <v>45000</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>45000</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>45021</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52873,7 +52873,7 @@
         <v>45043</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45042</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>45043</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45048</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45048</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>45048</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53225,7 +53225,7 @@
         <v>45051</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45054</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>45056</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         <v>45056</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53463,7 +53463,7 @@
         <v>45057</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53525,7 +53525,7 @@
         <v>45062</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45076</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45084</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45084</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45084</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>45087</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53887,7 +53887,7 @@
         <v>45089</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>45089</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54001,7 +54001,7 @@
         <v>45089</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45090</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54120,7 +54120,7 @@
         <v>45090</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>45092</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>45093</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45092</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54363,7 +54363,7 @@
         <v>45092</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54420,7 +54420,7 @@
         <v>45093</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>45093</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
         <v>45096</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>45096</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45098</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>45098</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54777,7 +54777,7 @@
         <v>45099</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>45103</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54901,7 +54901,7 @@
         <v>45104</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54963,7 +54963,7 @@
         <v>45104</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>45104</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         <v>45104</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55149,7 +55149,7 @@
         <v>45105</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45106</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>45107</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45112</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45112</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45113</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45113</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45113</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45115</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45115</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45117</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>45117</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45119</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>45119</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45119</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>45125</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56126,7 +56126,7 @@
         <v>45125</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45140</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56411,7 +56411,7 @@
         <v>45143</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45142</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45148</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45148</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56721,7 +56721,7 @@
         <v>45147</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>45147</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>45148</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>45147</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45148</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57031,7 +57031,7 @@
         <v>45148</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>45149</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57150,7 +57150,7 @@
         <v>45149</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>45149</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57336,7 +57336,7 @@
         <v>45150</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57398,7 +57398,7 @@
         <v>45150</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57460,7 +57460,7 @@
         <v>45150</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45150</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45150</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45150</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>45152</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57765,7 +57765,7 @@
         <v>45152</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57822,7 +57822,7 @@
         <v>45155</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>45154</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>45155</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58003,7 +58003,7 @@
         <v>45154</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58065,7 +58065,7 @@
         <v>45155</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>45155</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58179,7 +58179,7 @@
         <v>45156</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58236,7 +58236,7 @@
         <v>45158</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58293,7 +58293,7 @@
         <v>45159</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58350,7 +58350,7 @@
         <v>45161</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>45161</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45162</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58536,7 +58536,7 @@
         <v>45161</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -58593,7 +58593,7 @@
         <v>45163</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45166</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45170</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58774,7 +58774,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>45170</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>45171</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58955,7 +58955,7 @@
         <v>45171</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59017,7 +59017,7 @@
         <v>45171</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59079,7 +59079,7 @@
         <v>45171</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45171</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45171</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59265,7 +59265,7 @@
         <v>45170</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45173</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45177</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59446,7 +59446,7 @@
         <v>45177</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>45177</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>45186</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>45187</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>45187</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59741,7 +59741,7 @@
         <v>45188</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59803,7 +59803,7 @@
         <v>45187</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59865,7 +59865,7 @@
         <v>45188</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59922,7 +59922,7 @@
         <v>45189</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59984,7 +59984,7 @@
         <v>45189</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60046,7 +60046,7 @@
         <v>45190</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45190</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45190</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45194</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60398,7 +60398,7 @@
         <v>45194</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         <v>45195</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60517,7 +60517,7 @@
         <v>45195</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45196</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>45196</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60698,7 +60698,7 @@
         <v>45196</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60817,7 +60817,7 @@
         <v>45195</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45198</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60941,7 +60941,7 @@
         <v>45199</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>45199</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>45203</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45203</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61189,7 +61189,7 @@
         <v>45203</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61313,7 +61313,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>45205</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45205</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>45205</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45205</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61685,7 +61685,7 @@
         <v>45205</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>45207</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61809,7 +61809,7 @@
         <v>45207</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61871,7 +61871,7 @@
         <v>45207</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>45207</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61995,7 +61995,7 @@
         <v>45208</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>45209</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62114,7 +62114,7 @@
         <v>45210</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62171,7 +62171,7 @@
         <v>45212</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62233,7 +62233,7 @@
         <v>45212</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>45212</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         <v>45217</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>45217</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62481,7 +62481,7 @@
         <v>45217</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45217</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45217</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>45217</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45217</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45216</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62848,7 +62848,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62910,7 +62910,7 @@
         <v>45217</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45217</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>45218</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63096,7 +63096,7 @@
         <v>45222</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63158,7 +63158,7 @@
         <v>45223</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63220,7 +63220,7 @@
         <v>45224</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63282,7 +63282,7 @@
         <v>45225</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>45226</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63406,7 +63406,7 @@
         <v>45225</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63468,7 +63468,7 @@
         <v>45226</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63530,7 +63530,7 @@
         <v>45226</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>45226</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63654,7 +63654,7 @@
         <v>45226</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>45227</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45229</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45229</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63892,7 +63892,7 @@
         <v>45230</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -64006,7 +64006,7 @@
         <v>45232</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64063,7 +64063,7 @@
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64120,7 +64120,7 @@
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64234,7 +64234,7 @@
         <v>45232</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>45233</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64415,7 +64415,7 @@
         <v>45237</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64539,7 +64539,7 @@
         <v>45237</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64601,7 +64601,7 @@
         <v>45236</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>45237</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64725,7 +64725,7 @@
         <v>45238</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64787,7 +64787,7 @@
         <v>45238</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64849,7 +64849,7 @@
         <v>45238</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64911,7 +64911,7 @@
         <v>45238</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64973,7 +64973,7 @@
         <v>45238</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -65035,7 +65035,7 @@
         <v>45238</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65097,7 +65097,7 @@
         <v>45238</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>45238</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65221,7 +65221,7 @@
         <v>45238</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65283,7 +65283,7 @@
         <v>45238</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65340,7 +65340,7 @@
         <v>45238</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65402,7 +65402,7 @@
         <v>45239</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65459,7 +65459,7 @@
         <v>45239</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65516,7 +65516,7 @@
         <v>45239</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65573,7 +65573,7 @@
         <v>45239</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>45239</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65687,7 +65687,7 @@
         <v>45240</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65749,7 +65749,7 @@
         <v>45240</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65811,7 +65811,7 @@
         <v>45240</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65868,7 +65868,7 @@
         <v>45240</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>45243</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65982,7 +65982,7 @@
         <v>45243</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -66039,7 +66039,7 @@
         <v>45243</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66089,14 +66089,14 @@
     <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>A 57057-2023</t>
+          <t>A 57058-2023</t>
         </is>
       </c>
       <c r="B1019" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66109,7 +66109,7 @@
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -66146,14 +66146,14 @@
     <row r="1020" ht="15" customHeight="1">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>A 57058-2023</t>
+          <t>A 57057-2023</t>
         </is>
       </c>
       <c r="B1020" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66166,7 +66166,7 @@
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="H1020" t="n">
         <v>0</v>
@@ -66210,7 +66210,7 @@
         <v>45245</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66267,7 +66267,7 @@
         <v>45247</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66329,7 +66329,7 @@
         <v>45248</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66386,7 +66386,7 @@
         <v>45251</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66441,14 +66441,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 58756-2023</t>
+          <t>A 59110-2023</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66461,7 +66461,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>1.6</v>
+        <v>10.1</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -66498,14 +66498,14 @@
     <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>A 59117-2023</t>
+          <t>A 58756-2023</t>
         </is>
       </c>
       <c r="B1026" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66518,7 +66518,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -66555,14 +66555,14 @@
     <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 59110-2023</t>
+          <t>A 59117-2023</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66575,7 +66575,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -66619,7 +66619,7 @@
         <v>45251</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -66676,7 +66676,7 @@
         <v>45252</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66726,14 +66726,14 @@
     <row r="1030" ht="15" customHeight="1">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>A 59664-2023</t>
+          <t>A 60035-2023</t>
         </is>
       </c>
       <c r="B1030" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66745,13 +66745,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1030" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1030" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="H1030" t="n">
         <v>0</v>
@@ -66788,14 +66783,14 @@
     <row r="1031" ht="15" customHeight="1">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>A 59663-2023</t>
+          <t>A 59664-2023</t>
         </is>
       </c>
       <c r="B1031" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66813,7 +66808,7 @@
         </is>
       </c>
       <c r="G1031" t="n">
-        <v>12.8</v>
+        <v>3.3</v>
       </c>
       <c r="H1031" t="n">
         <v>0</v>
@@ -66850,14 +66845,14 @@
     <row r="1032" ht="15" customHeight="1">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>A 59671-2023</t>
+          <t>A 59663-2023</t>
         </is>
       </c>
       <c r="B1032" s="1" t="n">
-        <v>45255</v>
+        <v>45254</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66875,7 +66870,7 @@
         </is>
       </c>
       <c r="G1032" t="n">
-        <v>1.3</v>
+        <v>12.8</v>
       </c>
       <c r="H1032" t="n">
         <v>0</v>
@@ -66912,14 +66907,14 @@
     <row r="1033" ht="15" customHeight="1">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>A 60035-2023</t>
+          <t>A 59671-2023</t>
         </is>
       </c>
       <c r="B1033" s="1" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66931,8 +66926,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1033" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="H1033" t="n">
         <v>0</v>
@@ -66976,7 +66976,7 @@
         <v>45259</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67033,7 +67033,7 @@
         <v>45260</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -67090,7 +67090,7 @@
         <v>45260</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -67140,14 +67140,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 61780-2023</t>
+          <t>A 61778-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -67165,7 +67165,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -67202,14 +67202,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 61777-2023</t>
+          <t>A 61973-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -67221,13 +67221,8 @@
           <t>VILHELMINA</t>
         </is>
       </c>
-      <c r="F1038" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1038" t="n">
-        <v>20.6</v>
+        <v>24.9</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -67264,14 +67259,14 @@
     <row r="1039" ht="15" customHeight="1">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>A 61973-2023</t>
+          <t>A 61779-2023</t>
         </is>
       </c>
       <c r="B1039" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -67283,8 +67278,13 @@
           <t>VILHELMINA</t>
         </is>
       </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1039" t="n">
-        <v>24.9</v>
+        <v>2</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -67321,14 +67321,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 61778-2023</t>
+          <t>A 61780-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -67346,7 +67346,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -67383,14 +67383,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 62015-2023</t>
+          <t>A 62021-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -67403,7 +67403,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -67440,14 +67440,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 61779-2023</t>
+          <t>A 61777-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -67465,7 +67465,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>2</v>
+        <v>20.6</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -67499,62 +67499,176 @@
       </c>
       <c r="R1042" s="2" t="inlineStr"/>
     </row>
-    <row r="1043">
+    <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 62021-2023</t>
+          <t>A 62015-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1043" s="1" t="n">
+        <v>45273</v>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>VILHELMINA</t>
+        </is>
+      </c>
+      <c r="G1043" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1043" s="2" t="inlineStr"/>
+    </row>
+    <row r="1044" ht="15" customHeight="1">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>A 63050-2023</t>
+        </is>
+      </c>
+      <c r="B1044" s="1" t="n">
         <v>45272</v>
       </c>
-      <c r="D1043" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="E1043" t="inlineStr">
-        <is>
-          <t>VILHELMINA</t>
-        </is>
-      </c>
-      <c r="G1043" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H1043" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1043" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1043" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1043" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1043" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1043" t="n">
-        <v>0</v>
-      </c>
-      <c r="N1043" t="n">
-        <v>0</v>
-      </c>
-      <c r="O1043" t="n">
-        <v>0</v>
-      </c>
-      <c r="P1043" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q1043" t="n">
-        <v>0</v>
-      </c>
-      <c r="R1043" s="2" t="inlineStr"/>
+      <c r="C1044" s="1" t="n">
+        <v>45273</v>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>VILHELMINA</t>
+        </is>
+      </c>
+      <c r="G1044" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1044" s="2" t="inlineStr"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>A 63049-2023</t>
+        </is>
+      </c>
+      <c r="B1045" s="1" t="n">
+        <v>45272</v>
+      </c>
+      <c r="C1045" s="1" t="n">
+        <v>45273</v>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>VILHELMINA</t>
+        </is>
+      </c>
+      <c r="G1045" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1045" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1045"/>
+  <dimension ref="A1:Y1047"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44350</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>44972</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44753</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44118</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44494</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>44412</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>44644</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>44838</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>44074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44350</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45125</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>44494</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>43741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45154</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44266</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>44645</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45119</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>43731</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>44263</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>44412</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45050</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>44964</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45181</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45201</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45030</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45030</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>44522</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>44972</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45205</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44838</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>45054</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45201</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>43805</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44095</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44474</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44838</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>44945</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45156</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45201</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44838</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>43336</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44095</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44266</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44838</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45119</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45201</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45201</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>43781</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44361</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45119</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45201</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45205</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>43731</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44678</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45201</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45205</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>43336</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43983</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44211</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45149</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>43381</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>43677</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44000</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44664</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45125</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>45132</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>44199</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>45205</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45208</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43608</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43726</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44609</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45050</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44000</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44206</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>43432</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>43987</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44039</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44382</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44420</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44732</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44972</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45113</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43523</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43658</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>43731</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>43923</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43924</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44235</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>44309</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>44401</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44518</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>44648</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44781</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45098</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>45112</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45125</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45233</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>43741</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>43775</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>43833</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>43837</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44141</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44195</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44476</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44494</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44531</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44532</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44560</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44638</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>44827</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>44852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44960</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44964</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44972</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44994</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45105</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>45166</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45240</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43332</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43332</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>43335</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>43340</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>43340</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>43347</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43350</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43360</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43370</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43370</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43370</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43375</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43375</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43377</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43377</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43377</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43377</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>43377</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43377</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43384</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43384</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43389</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>43389</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>43389</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>43395</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>43402</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>43409</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>43412</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>43412</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>43418</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43432</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>43432</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>43432</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>43432</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43440</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43444</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43448</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43451</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43467</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43472</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43472</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43475</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43476</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43476</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43479</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43480</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>43480</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>43480</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>43487</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>43496</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>43497</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>43500</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>43501</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>43503</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>43507</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>43509</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43509</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43509</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43509</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43523</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43523</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43523</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>43523</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>43542</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>43542</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>43542</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>43545</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>43545</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>43545</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>43558</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>43559</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>43559</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>43564</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>43592</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>43592</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>43594</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>43594</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>43608</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>43608</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>43612</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>43613</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>43614</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>43614</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>43640</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>43640</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>43640</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>43640</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>43640</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>43641</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>43648</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>43648</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>43656</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>43661</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43661</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>43664</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43664</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43664</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43665</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43682</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43690</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43699</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43700</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>43703</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>43705</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43712</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43714</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>43721</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>43726</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>43728</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>43731</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>43733</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>43733</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>43733</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>43739</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>43741</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>43746</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>43749</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>43749</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>43753</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>43755</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>43762</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>43762</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>43765</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>43774</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>43775</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>43791</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>43803</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>43805</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>43808</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>43810</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>43815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>43833</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>43833</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>43833</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>43837</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>43837</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>43838</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>43838</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>43854</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>43858</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>43858</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>43896</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>43896</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>43896</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>43896</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>43909</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>43910</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>43913</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>43913</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>43913</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>43913</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>43913</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>43913</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>43913</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>43913</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>43914</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>43915</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>43915</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>43915</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>43915</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>43923</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>43923</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>43923</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>43927</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>43935</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>43944</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>43945</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>43964</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>43964</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>43966</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>43966</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>43977</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>43983</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>43983</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>43986</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>43986</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44000</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>44000</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44007</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44007</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44022</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44032</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44036</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44039</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44060</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44064</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44064</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44069</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44071</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44075</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>44078</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44088</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44092</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44092</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44092</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>44092</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44092</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>44097</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>44105</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>44105</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44109</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44118</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>44129</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>44144</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44151</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44153</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44154</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44155</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44161</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44162</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44162</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>44165</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44169</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44172</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>44186</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>44186</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44193</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44195</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44208</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44211</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>44211</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44211</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>44216</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44216</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44235</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44235</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44235</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44235</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44235</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44235</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44235</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44237</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>44243</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>44246</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>44253</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>44253</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>44266</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44307</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44307</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44307</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44307</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44307</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44316</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44316</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44328</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44330</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44341</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44341</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44350</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44356</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44357</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44361</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44361</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44361</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44361</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44370</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44371</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44371</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44371</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44371</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44377</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44378</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>44382</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44386</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44389</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44389</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>44389</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44389</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44397</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44406</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44412</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44420</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>44420</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>44420</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44420</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>44420</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>44420</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44420</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>44419</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>44426</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>44433</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>44434</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44442</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44442</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44443</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44442</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>44452</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44452</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44452</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44452</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44452</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>44453</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44461</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44461</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>44462</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44469</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44470</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44473</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>44476</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>44476</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>44481</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>44482</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>44482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>44482</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44484</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44485</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44488</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44488</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44489</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44491</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44496</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44498</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44500</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>44502</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44503</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>44505</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>44511</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44515</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44515</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44515</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44522</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44522</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>44525</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44529</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>44531</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>44531</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44532</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44532</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44532</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44532</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>44533</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>44537</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44540</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44543</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44545</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44545</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44545</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44545</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>44545</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>44545</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44564</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>44567</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>44568</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>44578</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>44578</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>44594</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>44604</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>44609</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>44609</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>44615</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44615</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44617</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44617</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>44617</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>44617</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44617</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>44619</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44619</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44619</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44619</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44621</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44621</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44622</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44623</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44625</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44627</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44627</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44628</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44628</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44628</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44628</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44637</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37067,7 +37